--- a/apostas/Bolao_Copa2026_TurimMFO_{Gustavo Marini).xlsx
+++ b/apostas/Bolao_Copa2026_TurimMFO_{Gustavo Marini).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gmarini\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pbrandao\Projetos\bolao-copa-2026\apostas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC1AE88-E3EA-4FFA-88ED-DA25470E86B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236CB02F-7D95-40FD-9013-53267C0231B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regras" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6771" uniqueCount="1618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6773" uniqueCount="1619">
   <si>
     <t>COMO FUNCIONA</t>
   </si>
@@ -4906,6 +4906,9 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>Danilo Santos</t>
   </si>
 </sst>
 </file>
@@ -6197,111 +6200,64 @@
     <xf numFmtId="0" fontId="48" fillId="52" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="45" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="46" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="44" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="49" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="47" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="50" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="48" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="49" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="51" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="48" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="41" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="42" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="55" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6324,63 +6280,110 @@
     <xf numFmtId="0" fontId="56" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="48" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="41" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="48" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="49" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="51" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="44" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="49" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="47" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="50" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="45" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6464,7 +6467,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0DFAB75F-7E28-4CC7-ABB6-A3E3AFD260A5}" name="TabelaConvocaveisCopa2026" displayName="TabelaConvocaveisCopa2026" ref="A1:B817">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0DFAB75F-7E28-4CC7-ABB6-A3E3AFD260A5}" name="TabelaConvocaveisCopa2026" displayName="TabelaConvocaveisCopa2026" ref="A1:B818">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6FA4FF17-BC0B-47E2-AC52-C82F6672760E}" name="Seleção"/>
     <tableColumn id="2" xr3:uid="{B9F79C32-6E6C-416F-9FFB-204743F546F8}" name="Jogador"/>
@@ -6762,25 +6765,25 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="B1:E44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="102.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="102.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="56.1" customHeight="1">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="174" t="s">
         <v>1596</v>
       </c>
-      <c r="C1" s="145"/>
-    </row>
-    <row r="2" spans="2:3" ht="27.95" customHeight="1">
-      <c r="B2" s="146" t="s">
+      <c r="C1" s="147"/>
+    </row>
+    <row r="2" spans="2:3" ht="27.9" customHeight="1">
+      <c r="B2" s="175" t="s">
         <v>745</v>
       </c>
-      <c r="C2" s="145"/>
+      <c r="C2" s="147"/>
     </row>
     <row r="3" spans="2:3" ht="24" customHeight="1">
       <c r="B3" s="1" t="s">
@@ -6794,7 +6797,7 @@
       <c r="B4" s="3" t="s">
         <v>1592</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="176" t="s">
         <v>1611</v>
       </c>
     </row>
@@ -6802,25 +6805,25 @@
       <c r="B5" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="C5" s="147"/>
+      <c r="C5" s="176"/>
     </row>
     <row r="6" spans="2:3" ht="27.75" customHeight="1">
       <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="147"/>
+      <c r="C6" s="176"/>
     </row>
     <row r="7" spans="2:3" ht="42" customHeight="1">
       <c r="B7" s="3" t="s">
         <v>1594</v>
       </c>
-      <c r="C7" s="147"/>
+      <c r="C7" s="176"/>
     </row>
     <row r="8" spans="2:3" ht="42" customHeight="1">
       <c r="B8" s="124" t="s">
         <v>1615</v>
       </c>
-      <c r="C8" s="147"/>
+      <c r="C8" s="176"/>
     </row>
     <row r="9" spans="2:3" ht="6" customHeight="1"/>
     <row r="10" spans="2:3" ht="24" customHeight="1">
@@ -6904,7 +6907,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="25.5">
+    <row r="23" spans="2:3" ht="26.4">
       <c r="B23" s="3" t="s">
         <v>1601</v>
       </c>
@@ -6914,7 +6917,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="25.5">
+    <row r="25" spans="2:3" ht="26.4">
       <c r="B25" s="124" t="s">
         <v>1603</v>
       </c>
@@ -7046,602 +7049,602 @@
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:EO34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="145" width="4.140625" customWidth="1"/>
+    <col min="2" max="145" width="4.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:145" ht="44.1" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="145"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="145"/>
-      <c r="Z1" s="145"/>
-      <c r="AA1" s="145"/>
-      <c r="AB1" s="145"/>
-      <c r="AC1" s="145"/>
-      <c r="AD1" s="145"/>
-      <c r="AE1" s="145"/>
-      <c r="AF1" s="145"/>
-      <c r="AG1" s="145"/>
-      <c r="AH1" s="145"/>
-      <c r="AI1" s="145"/>
-      <c r="AJ1" s="145"/>
-      <c r="AK1" s="145"/>
-      <c r="AL1" s="145"/>
-      <c r="AM1" s="145"/>
-      <c r="AN1" s="145"/>
-      <c r="AO1" s="145"/>
-      <c r="AP1" s="145"/>
-      <c r="AQ1" s="145"/>
-      <c r="AR1" s="145"/>
-      <c r="AS1" s="145"/>
-      <c r="AT1" s="145"/>
-      <c r="AU1" s="145"/>
-      <c r="AV1" s="145"/>
-      <c r="AW1" s="145"/>
-      <c r="AX1" s="145"/>
-      <c r="AY1" s="145"/>
-      <c r="AZ1" s="145"/>
-      <c r="BA1" s="145"/>
-      <c r="BB1" s="145"/>
-      <c r="BC1" s="145"/>
-      <c r="BD1" s="145"/>
-      <c r="BE1" s="145"/>
-      <c r="BF1" s="145"/>
-      <c r="BG1" s="145"/>
-      <c r="BH1" s="145"/>
-      <c r="BI1" s="145"/>
-      <c r="BJ1" s="145"/>
-      <c r="BK1" s="145"/>
-      <c r="BL1" s="145"/>
-      <c r="BM1" s="145"/>
-      <c r="BN1" s="145"/>
-      <c r="BO1" s="145"/>
-      <c r="BP1" s="145"/>
-      <c r="BQ1" s="145"/>
-      <c r="BR1" s="145"/>
-      <c r="BS1" s="145"/>
-      <c r="BT1" s="145"/>
-      <c r="BU1" s="145"/>
-      <c r="BV1" s="145"/>
-      <c r="BW1" s="145"/>
-      <c r="BX1" s="145"/>
-      <c r="BY1" s="145"/>
-      <c r="BZ1" s="145"/>
-      <c r="CA1" s="145"/>
-      <c r="CB1" s="145"/>
-      <c r="CC1" s="145"/>
-      <c r="CD1" s="145"/>
-      <c r="CE1" s="145"/>
-      <c r="CF1" s="145"/>
-      <c r="CG1" s="145"/>
-      <c r="CH1" s="145"/>
-      <c r="CI1" s="145"/>
-      <c r="CJ1" s="145"/>
-      <c r="CK1" s="145"/>
-      <c r="CL1" s="145"/>
-      <c r="CM1" s="145"/>
-      <c r="CN1" s="145"/>
-      <c r="CO1" s="145"/>
-      <c r="CP1" s="145"/>
-      <c r="CQ1" s="145"/>
-      <c r="CR1" s="145"/>
-      <c r="CS1" s="145"/>
-      <c r="CT1" s="145"/>
-      <c r="CU1" s="145"/>
-      <c r="CV1" s="145"/>
-      <c r="CW1" s="145"/>
-      <c r="CX1" s="145"/>
-      <c r="CY1" s="145"/>
-      <c r="CZ1" s="145"/>
-      <c r="DA1" s="145"/>
-      <c r="DB1" s="145"/>
-      <c r="DC1" s="145"/>
-      <c r="DD1" s="145"/>
-      <c r="DE1" s="145"/>
-      <c r="DF1" s="145"/>
-      <c r="DG1" s="145"/>
-      <c r="DH1" s="145"/>
-      <c r="DI1" s="145"/>
-      <c r="DJ1" s="145"/>
-      <c r="DK1" s="145"/>
-      <c r="DL1" s="145"/>
-      <c r="DM1" s="145"/>
-      <c r="DN1" s="145"/>
-      <c r="DO1" s="145"/>
-      <c r="DP1" s="145"/>
-      <c r="DQ1" s="145"/>
-      <c r="DR1" s="145"/>
-      <c r="DS1" s="145"/>
-      <c r="DT1" s="145"/>
-      <c r="DU1" s="145"/>
-      <c r="DV1" s="145"/>
-      <c r="DW1" s="145"/>
-      <c r="DX1" s="145"/>
-      <c r="DY1" s="145"/>
-      <c r="DZ1" s="145"/>
-      <c r="EA1" s="145"/>
-      <c r="EB1" s="145"/>
-      <c r="EC1" s="145"/>
-      <c r="ED1" s="145"/>
-      <c r="EE1" s="145"/>
-      <c r="EF1" s="145"/>
-      <c r="EG1" s="145"/>
-      <c r="EH1" s="145"/>
-      <c r="EI1" s="145"/>
-      <c r="EJ1" s="145"/>
-      <c r="EK1" s="145"/>
-      <c r="EL1" s="145"/>
-      <c r="EM1" s="145"/>
-      <c r="EN1" s="145"/>
-      <c r="EO1" s="145"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
+      <c r="Y1" s="147"/>
+      <c r="Z1" s="147"/>
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="147"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="147"/>
+      <c r="AH1" s="147"/>
+      <c r="AI1" s="147"/>
+      <c r="AJ1" s="147"/>
+      <c r="AK1" s="147"/>
+      <c r="AL1" s="147"/>
+      <c r="AM1" s="147"/>
+      <c r="AN1" s="147"/>
+      <c r="AO1" s="147"/>
+      <c r="AP1" s="147"/>
+      <c r="AQ1" s="147"/>
+      <c r="AR1" s="147"/>
+      <c r="AS1" s="147"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="147"/>
+      <c r="BA1" s="147"/>
+      <c r="BB1" s="147"/>
+      <c r="BC1" s="147"/>
+      <c r="BD1" s="147"/>
+      <c r="BE1" s="147"/>
+      <c r="BF1" s="147"/>
+      <c r="BG1" s="147"/>
+      <c r="BH1" s="147"/>
+      <c r="BI1" s="147"/>
+      <c r="BJ1" s="147"/>
+      <c r="BK1" s="147"/>
+      <c r="BL1" s="147"/>
+      <c r="BM1" s="147"/>
+      <c r="BN1" s="147"/>
+      <c r="BO1" s="147"/>
+      <c r="BP1" s="147"/>
+      <c r="BQ1" s="147"/>
+      <c r="BR1" s="147"/>
+      <c r="BS1" s="147"/>
+      <c r="BT1" s="147"/>
+      <c r="BU1" s="147"/>
+      <c r="BV1" s="147"/>
+      <c r="BW1" s="147"/>
+      <c r="BX1" s="147"/>
+      <c r="BY1" s="147"/>
+      <c r="BZ1" s="147"/>
+      <c r="CA1" s="147"/>
+      <c r="CB1" s="147"/>
+      <c r="CC1" s="147"/>
+      <c r="CD1" s="147"/>
+      <c r="CE1" s="147"/>
+      <c r="CF1" s="147"/>
+      <c r="CG1" s="147"/>
+      <c r="CH1" s="147"/>
+      <c r="CI1" s="147"/>
+      <c r="CJ1" s="147"/>
+      <c r="CK1" s="147"/>
+      <c r="CL1" s="147"/>
+      <c r="CM1" s="147"/>
+      <c r="CN1" s="147"/>
+      <c r="CO1" s="147"/>
+      <c r="CP1" s="147"/>
+      <c r="CQ1" s="147"/>
+      <c r="CR1" s="147"/>
+      <c r="CS1" s="147"/>
+      <c r="CT1" s="147"/>
+      <c r="CU1" s="147"/>
+      <c r="CV1" s="147"/>
+      <c r="CW1" s="147"/>
+      <c r="CX1" s="147"/>
+      <c r="CY1" s="147"/>
+      <c r="CZ1" s="147"/>
+      <c r="DA1" s="147"/>
+      <c r="DB1" s="147"/>
+      <c r="DC1" s="147"/>
+      <c r="DD1" s="147"/>
+      <c r="DE1" s="147"/>
+      <c r="DF1" s="147"/>
+      <c r="DG1" s="147"/>
+      <c r="DH1" s="147"/>
+      <c r="DI1" s="147"/>
+      <c r="DJ1" s="147"/>
+      <c r="DK1" s="147"/>
+      <c r="DL1" s="147"/>
+      <c r="DM1" s="147"/>
+      <c r="DN1" s="147"/>
+      <c r="DO1" s="147"/>
+      <c r="DP1" s="147"/>
+      <c r="DQ1" s="147"/>
+      <c r="DR1" s="147"/>
+      <c r="DS1" s="147"/>
+      <c r="DT1" s="147"/>
+      <c r="DU1" s="147"/>
+      <c r="DV1" s="147"/>
+      <c r="DW1" s="147"/>
+      <c r="DX1" s="147"/>
+      <c r="DY1" s="147"/>
+      <c r="DZ1" s="147"/>
+      <c r="EA1" s="147"/>
+      <c r="EB1" s="147"/>
+      <c r="EC1" s="147"/>
+      <c r="ED1" s="147"/>
+      <c r="EE1" s="147"/>
+      <c r="EF1" s="147"/>
+      <c r="EG1" s="147"/>
+      <c r="EH1" s="147"/>
+      <c r="EI1" s="147"/>
+      <c r="EJ1" s="147"/>
+      <c r="EK1" s="147"/>
+      <c r="EL1" s="147"/>
+      <c r="EM1" s="147"/>
+      <c r="EN1" s="147"/>
+      <c r="EO1" s="147"/>
     </row>
     <row r="2" spans="1:145" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="145"/>
-      <c r="L2" s="145"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="145"/>
-      <c r="O2" s="145"/>
-      <c r="P2" s="145"/>
-      <c r="Q2" s="145"/>
-      <c r="R2" s="145"/>
-      <c r="S2" s="145"/>
-      <c r="T2" s="145"/>
-      <c r="U2" s="145"/>
-      <c r="V2" s="145"/>
-      <c r="W2" s="145"/>
-      <c r="X2" s="145"/>
-      <c r="Y2" s="145"/>
-      <c r="Z2" s="145"/>
-      <c r="AA2" s="145"/>
-      <c r="AB2" s="145"/>
-      <c r="AC2" s="145"/>
-      <c r="AD2" s="145"/>
-      <c r="AE2" s="145"/>
-      <c r="AF2" s="145"/>
-      <c r="AG2" s="145"/>
-      <c r="AH2" s="145"/>
-      <c r="AI2" s="145"/>
-      <c r="AJ2" s="145"/>
-      <c r="AK2" s="145"/>
-      <c r="AL2" s="145"/>
-      <c r="AM2" s="145"/>
-      <c r="AN2" s="145"/>
-      <c r="AO2" s="145"/>
-      <c r="AP2" s="145"/>
-      <c r="AQ2" s="145"/>
-      <c r="AR2" s="145"/>
-      <c r="AS2" s="145"/>
-      <c r="AT2" s="145"/>
-      <c r="AU2" s="145"/>
-      <c r="AV2" s="145"/>
-      <c r="AW2" s="145"/>
-      <c r="AX2" s="145"/>
-      <c r="AY2" s="145"/>
-      <c r="AZ2" s="145"/>
-      <c r="BA2" s="145"/>
-      <c r="BB2" s="145"/>
-      <c r="BC2" s="145"/>
-      <c r="BD2" s="145"/>
-      <c r="BE2" s="145"/>
-      <c r="BF2" s="145"/>
-      <c r="BG2" s="145"/>
-      <c r="BH2" s="145"/>
-      <c r="BI2" s="145"/>
-      <c r="BJ2" s="145"/>
-      <c r="BK2" s="145"/>
-      <c r="BL2" s="145"/>
-      <c r="BM2" s="145"/>
-      <c r="BN2" s="145"/>
-      <c r="BO2" s="145"/>
-      <c r="BP2" s="145"/>
-      <c r="BQ2" s="145"/>
-      <c r="BR2" s="145"/>
-      <c r="BS2" s="145"/>
-      <c r="BT2" s="145"/>
-      <c r="BU2" s="145"/>
-      <c r="BV2" s="145"/>
-      <c r="BW2" s="145"/>
-      <c r="BX2" s="145"/>
-      <c r="BY2" s="145"/>
-      <c r="BZ2" s="145"/>
-      <c r="CA2" s="145"/>
-      <c r="CB2" s="145"/>
-      <c r="CC2" s="145"/>
-      <c r="CD2" s="145"/>
-      <c r="CE2" s="145"/>
-      <c r="CF2" s="145"/>
-      <c r="CG2" s="145"/>
-      <c r="CH2" s="145"/>
-      <c r="CI2" s="145"/>
-      <c r="CJ2" s="145"/>
-      <c r="CK2" s="145"/>
-      <c r="CL2" s="145"/>
-      <c r="CM2" s="145"/>
-      <c r="CN2" s="145"/>
-      <c r="CO2" s="145"/>
-      <c r="CP2" s="145"/>
-      <c r="CQ2" s="145"/>
-      <c r="CR2" s="145"/>
-      <c r="CS2" s="145"/>
-      <c r="CT2" s="145"/>
-      <c r="CU2" s="145"/>
-      <c r="CV2" s="145"/>
-      <c r="CW2" s="145"/>
-      <c r="CX2" s="145"/>
-      <c r="CY2" s="145"/>
-      <c r="CZ2" s="145"/>
-      <c r="DA2" s="145"/>
-      <c r="DB2" s="145"/>
-      <c r="DC2" s="145"/>
-      <c r="DD2" s="145"/>
-      <c r="DE2" s="145"/>
-      <c r="DF2" s="145"/>
-      <c r="DG2" s="145"/>
-      <c r="DH2" s="145"/>
-      <c r="DI2" s="145"/>
-      <c r="DJ2" s="145"/>
-      <c r="DK2" s="145"/>
-      <c r="DL2" s="145"/>
-      <c r="DM2" s="145"/>
-      <c r="DN2" s="145"/>
-      <c r="DO2" s="145"/>
-      <c r="DP2" s="145"/>
-      <c r="DQ2" s="145"/>
-      <c r="DR2" s="145"/>
-      <c r="DS2" s="145"/>
-      <c r="DT2" s="145"/>
-      <c r="DU2" s="145"/>
-      <c r="DV2" s="145"/>
-      <c r="DW2" s="145"/>
-      <c r="DX2" s="145"/>
-      <c r="DY2" s="145"/>
-      <c r="DZ2" s="145"/>
-      <c r="EA2" s="145"/>
-      <c r="EB2" s="145"/>
-      <c r="EC2" s="145"/>
-      <c r="ED2" s="145"/>
-      <c r="EE2" s="145"/>
-      <c r="EF2" s="145"/>
-      <c r="EG2" s="145"/>
-      <c r="EH2" s="145"/>
-      <c r="EI2" s="145"/>
-      <c r="EJ2" s="145"/>
-      <c r="EK2" s="145"/>
-      <c r="EL2" s="145"/>
-      <c r="EM2" s="145"/>
-      <c r="EN2" s="145"/>
-      <c r="EO2" s="145"/>
-    </row>
-    <row r="3" spans="1:145" ht="27.95" customHeight="1">
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="147"/>
+      <c r="T2" s="147"/>
+      <c r="U2" s="147"/>
+      <c r="V2" s="147"/>
+      <c r="W2" s="147"/>
+      <c r="X2" s="147"/>
+      <c r="Y2" s="147"/>
+      <c r="Z2" s="147"/>
+      <c r="AA2" s="147"/>
+      <c r="AB2" s="147"/>
+      <c r="AC2" s="147"/>
+      <c r="AD2" s="147"/>
+      <c r="AE2" s="147"/>
+      <c r="AF2" s="147"/>
+      <c r="AG2" s="147"/>
+      <c r="AH2" s="147"/>
+      <c r="AI2" s="147"/>
+      <c r="AJ2" s="147"/>
+      <c r="AK2" s="147"/>
+      <c r="AL2" s="147"/>
+      <c r="AM2" s="147"/>
+      <c r="AN2" s="147"/>
+      <c r="AO2" s="147"/>
+      <c r="AP2" s="147"/>
+      <c r="AQ2" s="147"/>
+      <c r="AR2" s="147"/>
+      <c r="AS2" s="147"/>
+      <c r="AT2" s="147"/>
+      <c r="AU2" s="147"/>
+      <c r="AV2" s="147"/>
+      <c r="AW2" s="147"/>
+      <c r="AX2" s="147"/>
+      <c r="AY2" s="147"/>
+      <c r="AZ2" s="147"/>
+      <c r="BA2" s="147"/>
+      <c r="BB2" s="147"/>
+      <c r="BC2" s="147"/>
+      <c r="BD2" s="147"/>
+      <c r="BE2" s="147"/>
+      <c r="BF2" s="147"/>
+      <c r="BG2" s="147"/>
+      <c r="BH2" s="147"/>
+      <c r="BI2" s="147"/>
+      <c r="BJ2" s="147"/>
+      <c r="BK2" s="147"/>
+      <c r="BL2" s="147"/>
+      <c r="BM2" s="147"/>
+      <c r="BN2" s="147"/>
+      <c r="BO2" s="147"/>
+      <c r="BP2" s="147"/>
+      <c r="BQ2" s="147"/>
+      <c r="BR2" s="147"/>
+      <c r="BS2" s="147"/>
+      <c r="BT2" s="147"/>
+      <c r="BU2" s="147"/>
+      <c r="BV2" s="147"/>
+      <c r="BW2" s="147"/>
+      <c r="BX2" s="147"/>
+      <c r="BY2" s="147"/>
+      <c r="BZ2" s="147"/>
+      <c r="CA2" s="147"/>
+      <c r="CB2" s="147"/>
+      <c r="CC2" s="147"/>
+      <c r="CD2" s="147"/>
+      <c r="CE2" s="147"/>
+      <c r="CF2" s="147"/>
+      <c r="CG2" s="147"/>
+      <c r="CH2" s="147"/>
+      <c r="CI2" s="147"/>
+      <c r="CJ2" s="147"/>
+      <c r="CK2" s="147"/>
+      <c r="CL2" s="147"/>
+      <c r="CM2" s="147"/>
+      <c r="CN2" s="147"/>
+      <c r="CO2" s="147"/>
+      <c r="CP2" s="147"/>
+      <c r="CQ2" s="147"/>
+      <c r="CR2" s="147"/>
+      <c r="CS2" s="147"/>
+      <c r="CT2" s="147"/>
+      <c r="CU2" s="147"/>
+      <c r="CV2" s="147"/>
+      <c r="CW2" s="147"/>
+      <c r="CX2" s="147"/>
+      <c r="CY2" s="147"/>
+      <c r="CZ2" s="147"/>
+      <c r="DA2" s="147"/>
+      <c r="DB2" s="147"/>
+      <c r="DC2" s="147"/>
+      <c r="DD2" s="147"/>
+      <c r="DE2" s="147"/>
+      <c r="DF2" s="147"/>
+      <c r="DG2" s="147"/>
+      <c r="DH2" s="147"/>
+      <c r="DI2" s="147"/>
+      <c r="DJ2" s="147"/>
+      <c r="DK2" s="147"/>
+      <c r="DL2" s="147"/>
+      <c r="DM2" s="147"/>
+      <c r="DN2" s="147"/>
+      <c r="DO2" s="147"/>
+      <c r="DP2" s="147"/>
+      <c r="DQ2" s="147"/>
+      <c r="DR2" s="147"/>
+      <c r="DS2" s="147"/>
+      <c r="DT2" s="147"/>
+      <c r="DU2" s="147"/>
+      <c r="DV2" s="147"/>
+      <c r="DW2" s="147"/>
+      <c r="DX2" s="147"/>
+      <c r="DY2" s="147"/>
+      <c r="DZ2" s="147"/>
+      <c r="EA2" s="147"/>
+      <c r="EB2" s="147"/>
+      <c r="EC2" s="147"/>
+      <c r="ED2" s="147"/>
+      <c r="EE2" s="147"/>
+      <c r="EF2" s="147"/>
+      <c r="EG2" s="147"/>
+      <c r="EH2" s="147"/>
+      <c r="EI2" s="147"/>
+      <c r="EJ2" s="147"/>
+      <c r="EK2" s="147"/>
+      <c r="EL2" s="147"/>
+      <c r="EM2" s="147"/>
+      <c r="EN2" s="147"/>
+      <c r="EO2" s="147"/>
+    </row>
+    <row r="3" spans="1:145" ht="27.9" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="148" t="s">
+      <c r="B3" s="181" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="145"/>
-      <c r="D3" s="148" t="s">
+      <c r="C3" s="147"/>
+      <c r="D3" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="145"/>
-      <c r="F3" s="148" t="s">
+      <c r="E3" s="147"/>
+      <c r="F3" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="145"/>
-      <c r="H3" s="148" t="s">
+      <c r="G3" s="147"/>
+      <c r="H3" s="181" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="145"/>
-      <c r="J3" s="148" t="s">
+      <c r="I3" s="147"/>
+      <c r="J3" s="181" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="145"/>
-      <c r="L3" s="148" t="s">
+      <c r="K3" s="147"/>
+      <c r="L3" s="181" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="145"/>
-      <c r="N3" s="151" t="s">
+      <c r="M3" s="147"/>
+      <c r="N3" s="189" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="145"/>
-      <c r="P3" s="151" t="s">
+      <c r="O3" s="147"/>
+      <c r="P3" s="189" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="151" t="s">
+      <c r="Q3" s="147"/>
+      <c r="R3" s="189" t="s">
         <v>43</v>
       </c>
-      <c r="S3" s="145"/>
-      <c r="T3" s="151" t="s">
+      <c r="S3" s="147"/>
+      <c r="T3" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="145"/>
-      <c r="V3" s="151" t="s">
+      <c r="U3" s="147"/>
+      <c r="V3" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="W3" s="145"/>
-      <c r="X3" s="151" t="s">
+      <c r="W3" s="147"/>
+      <c r="X3" s="189" t="s">
         <v>46</v>
       </c>
-      <c r="Y3" s="145"/>
-      <c r="Z3" s="172" t="s">
+      <c r="Y3" s="147"/>
+      <c r="Z3" s="192" t="s">
         <v>47</v>
       </c>
-      <c r="AA3" s="145"/>
-      <c r="AB3" s="172" t="s">
+      <c r="AA3" s="147"/>
+      <c r="AB3" s="192" t="s">
         <v>48</v>
       </c>
-      <c r="AC3" s="145"/>
-      <c r="AD3" s="172" t="s">
+      <c r="AC3" s="147"/>
+      <c r="AD3" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="AE3" s="145"/>
-      <c r="AF3" s="172" t="s">
+      <c r="AE3" s="147"/>
+      <c r="AF3" s="192" t="s">
         <v>50</v>
       </c>
-      <c r="AG3" s="145"/>
-      <c r="AH3" s="172" t="s">
+      <c r="AG3" s="147"/>
+      <c r="AH3" s="192" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="145"/>
-      <c r="AJ3" s="172" t="s">
+      <c r="AI3" s="147"/>
+      <c r="AJ3" s="192" t="s">
         <v>52</v>
       </c>
-      <c r="AK3" s="145"/>
-      <c r="AL3" s="149" t="s">
+      <c r="AK3" s="147"/>
+      <c r="AL3" s="191" t="s">
         <v>53</v>
       </c>
-      <c r="AM3" s="145"/>
-      <c r="AN3" s="149" t="s">
+      <c r="AM3" s="147"/>
+      <c r="AN3" s="191" t="s">
         <v>54</v>
       </c>
-      <c r="AO3" s="145"/>
-      <c r="AP3" s="149" t="s">
+      <c r="AO3" s="147"/>
+      <c r="AP3" s="191" t="s">
         <v>55</v>
       </c>
-      <c r="AQ3" s="145"/>
-      <c r="AR3" s="149" t="s">
+      <c r="AQ3" s="147"/>
+      <c r="AR3" s="191" t="s">
         <v>56</v>
       </c>
-      <c r="AS3" s="145"/>
-      <c r="AT3" s="149" t="s">
+      <c r="AS3" s="147"/>
+      <c r="AT3" s="191" t="s">
         <v>57</v>
       </c>
-      <c r="AU3" s="145"/>
-      <c r="AV3" s="149" t="s">
+      <c r="AU3" s="147"/>
+      <c r="AV3" s="191" t="s">
         <v>58</v>
       </c>
-      <c r="AW3" s="145"/>
-      <c r="AX3" s="150" t="s">
+      <c r="AW3" s="147"/>
+      <c r="AX3" s="183" t="s">
         <v>59</v>
       </c>
-      <c r="AY3" s="145"/>
-      <c r="AZ3" s="150" t="s">
+      <c r="AY3" s="147"/>
+      <c r="AZ3" s="183" t="s">
         <v>60</v>
       </c>
-      <c r="BA3" s="145"/>
-      <c r="BB3" s="150" t="s">
+      <c r="BA3" s="147"/>
+      <c r="BB3" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="BC3" s="145"/>
-      <c r="BD3" s="150" t="s">
+      <c r="BC3" s="147"/>
+      <c r="BD3" s="183" t="s">
         <v>62</v>
       </c>
-      <c r="BE3" s="145"/>
-      <c r="BF3" s="150" t="s">
+      <c r="BE3" s="147"/>
+      <c r="BF3" s="183" t="s">
         <v>63</v>
       </c>
-      <c r="BG3" s="145"/>
-      <c r="BH3" s="150" t="s">
+      <c r="BG3" s="147"/>
+      <c r="BH3" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="BI3" s="145"/>
-      <c r="BJ3" s="153" t="s">
+      <c r="BI3" s="147"/>
+      <c r="BJ3" s="184" t="s">
         <v>65</v>
       </c>
-      <c r="BK3" s="145"/>
-      <c r="BL3" s="153" t="s">
+      <c r="BK3" s="147"/>
+      <c r="BL3" s="184" t="s">
         <v>66</v>
       </c>
-      <c r="BM3" s="145"/>
-      <c r="BN3" s="153" t="s">
+      <c r="BM3" s="147"/>
+      <c r="BN3" s="184" t="s">
         <v>67</v>
       </c>
-      <c r="BO3" s="145"/>
-      <c r="BP3" s="153" t="s">
+      <c r="BO3" s="147"/>
+      <c r="BP3" s="184" t="s">
         <v>68</v>
       </c>
-      <c r="BQ3" s="145"/>
-      <c r="BR3" s="153" t="s">
+      <c r="BQ3" s="147"/>
+      <c r="BR3" s="184" t="s">
         <v>69</v>
       </c>
-      <c r="BS3" s="145"/>
-      <c r="BT3" s="153" t="s">
+      <c r="BS3" s="147"/>
+      <c r="BT3" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="BU3" s="145"/>
-      <c r="BV3" s="154" t="s">
+      <c r="BU3" s="147"/>
+      <c r="BV3" s="199" t="s">
         <v>71</v>
       </c>
-      <c r="BW3" s="145"/>
-      <c r="BX3" s="154" t="s">
+      <c r="BW3" s="147"/>
+      <c r="BX3" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="BY3" s="145"/>
-      <c r="BZ3" s="154" t="s">
+      <c r="BY3" s="147"/>
+      <c r="BZ3" s="199" t="s">
         <v>73</v>
       </c>
-      <c r="CA3" s="145"/>
-      <c r="CB3" s="154" t="s">
+      <c r="CA3" s="147"/>
+      <c r="CB3" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="CC3" s="145"/>
-      <c r="CD3" s="154" t="s">
+      <c r="CC3" s="147"/>
+      <c r="CD3" s="199" t="s">
         <v>75</v>
       </c>
-      <c r="CE3" s="145"/>
-      <c r="CF3" s="154" t="s">
+      <c r="CE3" s="147"/>
+      <c r="CF3" s="199" t="s">
         <v>76</v>
       </c>
-      <c r="CG3" s="145"/>
-      <c r="CH3" s="157" t="s">
+      <c r="CG3" s="147"/>
+      <c r="CH3" s="195" t="s">
         <v>77</v>
       </c>
-      <c r="CI3" s="145"/>
-      <c r="CJ3" s="157" t="s">
+      <c r="CI3" s="147"/>
+      <c r="CJ3" s="195" t="s">
         <v>78</v>
       </c>
-      <c r="CK3" s="145"/>
-      <c r="CL3" s="157" t="s">
+      <c r="CK3" s="147"/>
+      <c r="CL3" s="195" t="s">
         <v>79</v>
       </c>
-      <c r="CM3" s="145"/>
-      <c r="CN3" s="157" t="s">
+      <c r="CM3" s="147"/>
+      <c r="CN3" s="195" t="s">
         <v>80</v>
       </c>
-      <c r="CO3" s="145"/>
-      <c r="CP3" s="157" t="s">
+      <c r="CO3" s="147"/>
+      <c r="CP3" s="195" t="s">
         <v>81</v>
       </c>
-      <c r="CQ3" s="145"/>
-      <c r="CR3" s="157" t="s">
+      <c r="CQ3" s="147"/>
+      <c r="CR3" s="195" t="s">
         <v>82</v>
       </c>
-      <c r="CS3" s="145"/>
-      <c r="CT3" s="158" t="s">
+      <c r="CS3" s="147"/>
+      <c r="CT3" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="CU3" s="145"/>
-      <c r="CV3" s="158" t="s">
+      <c r="CU3" s="147"/>
+      <c r="CV3" s="178" t="s">
         <v>84</v>
       </c>
-      <c r="CW3" s="145"/>
-      <c r="CX3" s="158" t="s">
+      <c r="CW3" s="147"/>
+      <c r="CX3" s="178" t="s">
         <v>85</v>
       </c>
-      <c r="CY3" s="145"/>
-      <c r="CZ3" s="158" t="s">
+      <c r="CY3" s="147"/>
+      <c r="CZ3" s="178" t="s">
         <v>86</v>
       </c>
-      <c r="DA3" s="145"/>
-      <c r="DB3" s="158" t="s">
+      <c r="DA3" s="147"/>
+      <c r="DB3" s="178" t="s">
         <v>87</v>
       </c>
-      <c r="DC3" s="145"/>
-      <c r="DD3" s="158" t="s">
+      <c r="DC3" s="147"/>
+      <c r="DD3" s="178" t="s">
         <v>88</v>
       </c>
-      <c r="DE3" s="145"/>
-      <c r="DF3" s="161" t="s">
+      <c r="DE3" s="147"/>
+      <c r="DF3" s="198" t="s">
         <v>89</v>
       </c>
-      <c r="DG3" s="145"/>
-      <c r="DH3" s="161" t="s">
+      <c r="DG3" s="147"/>
+      <c r="DH3" s="198" t="s">
         <v>90</v>
       </c>
-      <c r="DI3" s="145"/>
-      <c r="DJ3" s="161" t="s">
+      <c r="DI3" s="147"/>
+      <c r="DJ3" s="198" t="s">
         <v>91</v>
       </c>
-      <c r="DK3" s="145"/>
-      <c r="DL3" s="161" t="s">
+      <c r="DK3" s="147"/>
+      <c r="DL3" s="198" t="s">
         <v>92</v>
       </c>
-      <c r="DM3" s="145"/>
-      <c r="DN3" s="161" t="s">
+      <c r="DM3" s="147"/>
+      <c r="DN3" s="198" t="s">
         <v>93</v>
       </c>
-      <c r="DO3" s="145"/>
-      <c r="DP3" s="161" t="s">
+      <c r="DO3" s="147"/>
+      <c r="DP3" s="198" t="s">
         <v>94</v>
       </c>
-      <c r="DQ3" s="145"/>
-      <c r="DR3" s="160" t="s">
+      <c r="DQ3" s="147"/>
+      <c r="DR3" s="188" t="s">
         <v>95</v>
       </c>
-      <c r="DS3" s="145"/>
-      <c r="DT3" s="160" t="s">
+      <c r="DS3" s="147"/>
+      <c r="DT3" s="188" t="s">
         <v>96</v>
       </c>
-      <c r="DU3" s="145"/>
-      <c r="DV3" s="160" t="s">
+      <c r="DU3" s="147"/>
+      <c r="DV3" s="188" t="s">
         <v>97</v>
       </c>
-      <c r="DW3" s="145"/>
-      <c r="DX3" s="160" t="s">
+      <c r="DW3" s="147"/>
+      <c r="DX3" s="188" t="s">
         <v>98</v>
       </c>
-      <c r="DY3" s="145"/>
-      <c r="DZ3" s="160" t="s">
+      <c r="DY3" s="147"/>
+      <c r="DZ3" s="188" t="s">
         <v>99</v>
       </c>
-      <c r="EA3" s="145"/>
-      <c r="EB3" s="160" t="s">
+      <c r="EA3" s="147"/>
+      <c r="EB3" s="188" t="s">
         <v>100</v>
       </c>
-      <c r="EC3" s="145"/>
-      <c r="ED3" s="156" t="s">
+      <c r="EC3" s="147"/>
+      <c r="ED3" s="177" t="s">
         <v>101</v>
       </c>
-      <c r="EE3" s="145"/>
-      <c r="EF3" s="156" t="s">
+      <c r="EE3" s="147"/>
+      <c r="EF3" s="177" t="s">
         <v>102</v>
       </c>
-      <c r="EG3" s="145"/>
-      <c r="EH3" s="156" t="s">
+      <c r="EG3" s="147"/>
+      <c r="EH3" s="177" t="s">
         <v>103</v>
       </c>
-      <c r="EI3" s="145"/>
-      <c r="EJ3" s="156" t="s">
+      <c r="EI3" s="147"/>
+      <c r="EJ3" s="177" t="s">
         <v>104</v>
       </c>
-      <c r="EK3" s="145"/>
-      <c r="EL3" s="156" t="s">
+      <c r="EK3" s="147"/>
+      <c r="EL3" s="177" t="s">
         <v>105</v>
       </c>
-      <c r="EM3" s="145"/>
-      <c r="EN3" s="156" t="s">
+      <c r="EM3" s="147"/>
+      <c r="EN3" s="177" t="s">
         <v>106</v>
       </c>
-      <c r="EO3" s="145"/>
+      <c r="EO3" s="147"/>
     </row>
     <row r="4" spans="1:145" ht="26.1" customHeight="1">
       <c r="A4" s="18" t="s">
@@ -8517,123 +8520,123 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:145" ht="21.95" customHeight="1">
-      <c r="A7" s="177" t="s">
+    <row r="7" spans="1:145" ht="21.9" customHeight="1">
+      <c r="A7" s="179" t="s">
         <v>1598</v>
       </c>
-      <c r="B7" s="145"/>
-      <c r="C7" s="145"/>
-      <c r="D7" s="145"/>
-      <c r="E7" s="145"/>
-      <c r="F7" s="145"/>
-      <c r="G7" s="145"/>
-      <c r="H7" s="145"/>
-      <c r="I7" s="145"/>
-      <c r="J7" s="145"/>
-      <c r="K7" s="145"/>
-      <c r="L7" s="145"/>
-      <c r="M7" s="145"/>
-      <c r="N7" s="145"/>
-      <c r="O7" s="145"/>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145"/>
-      <c r="R7" s="145"/>
-      <c r="S7" s="145"/>
-      <c r="T7" s="145"/>
-      <c r="U7" s="145"/>
-      <c r="V7" s="145"/>
-      <c r="W7" s="145"/>
-      <c r="X7" s="145"/>
-      <c r="Y7" s="145"/>
-      <c r="Z7" s="145"/>
-      <c r="AA7" s="145"/>
-      <c r="AB7" s="145"/>
-      <c r="AC7" s="145"/>
-      <c r="AD7" s="145"/>
-      <c r="AE7" s="145"/>
-      <c r="AF7" s="145"/>
-      <c r="AG7" s="145"/>
-      <c r="AH7" s="145"/>
-      <c r="AI7" s="145"/>
-      <c r="AJ7" s="145"/>
-      <c r="AK7" s="145"/>
-      <c r="AL7" s="145"/>
-      <c r="AM7" s="145"/>
-      <c r="AN7" s="145"/>
-      <c r="AO7" s="145"/>
-      <c r="AP7" s="145"/>
-      <c r="AQ7" s="145"/>
-      <c r="AR7" s="145"/>
-      <c r="AS7" s="145"/>
-      <c r="AT7" s="145"/>
-      <c r="AU7" s="145"/>
-      <c r="AV7" s="145"/>
-    </row>
-    <row r="8" spans="1:145" ht="21.95" customHeight="1">
-      <c r="A8" s="171" t="s">
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="147"/>
+      <c r="U7" s="147"/>
+      <c r="V7" s="147"/>
+      <c r="W7" s="147"/>
+      <c r="X7" s="147"/>
+      <c r="Y7" s="147"/>
+      <c r="Z7" s="147"/>
+      <c r="AA7" s="147"/>
+      <c r="AB7" s="147"/>
+      <c r="AC7" s="147"/>
+      <c r="AD7" s="147"/>
+      <c r="AE7" s="147"/>
+      <c r="AF7" s="147"/>
+      <c r="AG7" s="147"/>
+      <c r="AH7" s="147"/>
+      <c r="AI7" s="147"/>
+      <c r="AJ7" s="147"/>
+      <c r="AK7" s="147"/>
+      <c r="AL7" s="147"/>
+      <c r="AM7" s="147"/>
+      <c r="AN7" s="147"/>
+      <c r="AO7" s="147"/>
+      <c r="AP7" s="147"/>
+      <c r="AQ7" s="147"/>
+      <c r="AR7" s="147"/>
+      <c r="AS7" s="147"/>
+      <c r="AT7" s="147"/>
+      <c r="AU7" s="147"/>
+      <c r="AV7" s="147"/>
+    </row>
+    <row r="8" spans="1:145" ht="21.9" customHeight="1">
+      <c r="A8" s="200" t="s">
         <v>156</v>
       </c>
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
-      <c r="D8" s="145"/>
-      <c r="E8" s="145"/>
-      <c r="F8" s="145"/>
-      <c r="G8" s="145"/>
-      <c r="H8" s="145"/>
-      <c r="I8" s="145"/>
-      <c r="J8" s="145"/>
-      <c r="K8" s="145"/>
-      <c r="L8" s="145"/>
-      <c r="M8" s="145"/>
-      <c r="N8" s="145"/>
-      <c r="O8" s="145"/>
-      <c r="Q8" s="166" t="s">
+      <c r="B8" s="147"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="147"/>
+      <c r="H8" s="147"/>
+      <c r="I8" s="147"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="O8" s="147"/>
+      <c r="Q8" s="201" t="s">
         <v>157</v>
       </c>
-      <c r="R8" s="145"/>
-      <c r="S8" s="145"/>
-      <c r="T8" s="145"/>
-      <c r="U8" s="145"/>
-      <c r="V8" s="145"/>
-      <c r="W8" s="145"/>
-      <c r="X8" s="145"/>
-      <c r="Y8" s="145"/>
-      <c r="Z8" s="145"/>
-      <c r="AA8" s="145"/>
-      <c r="AB8" s="145"/>
-      <c r="AC8" s="145"/>
-      <c r="AD8" s="145"/>
-      <c r="AE8" s="145"/>
-      <c r="AG8" s="159" t="s">
+      <c r="R8" s="147"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="147"/>
+      <c r="U8" s="147"/>
+      <c r="V8" s="147"/>
+      <c r="W8" s="147"/>
+      <c r="X8" s="147"/>
+      <c r="Y8" s="147"/>
+      <c r="Z8" s="147"/>
+      <c r="AA8" s="147"/>
+      <c r="AB8" s="147"/>
+      <c r="AC8" s="147"/>
+      <c r="AD8" s="147"/>
+      <c r="AE8" s="147"/>
+      <c r="AG8" s="204" t="s">
         <v>158</v>
       </c>
-      <c r="AH8" s="145"/>
-      <c r="AI8" s="145"/>
-      <c r="AJ8" s="145"/>
-      <c r="AK8" s="145"/>
-      <c r="AL8" s="145"/>
-      <c r="AM8" s="145"/>
-      <c r="AN8" s="145"/>
-      <c r="AO8" s="145"/>
-      <c r="AP8" s="145"/>
-      <c r="AQ8" s="145"/>
-      <c r="AR8" s="145"/>
-      <c r="AS8" s="145"/>
-      <c r="AT8" s="145"/>
-      <c r="AU8" s="145"/>
+      <c r="AH8" s="147"/>
+      <c r="AI8" s="147"/>
+      <c r="AJ8" s="147"/>
+      <c r="AK8" s="147"/>
+      <c r="AL8" s="147"/>
+      <c r="AM8" s="147"/>
+      <c r="AN8" s="147"/>
+      <c r="AO8" s="147"/>
+      <c r="AP8" s="147"/>
+      <c r="AQ8" s="147"/>
+      <c r="AR8" s="147"/>
+      <c r="AS8" s="147"/>
+      <c r="AT8" s="147"/>
+      <c r="AU8" s="147"/>
     </row>
     <row r="9" spans="1:145" ht="18" customHeight="1">
       <c r="A9" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="167" t="s">
+      <c r="B9" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="C9" s="145"/>
-      <c r="D9" s="145"/>
-      <c r="E9" s="145"/>
-      <c r="F9" s="145"/>
-      <c r="G9" s="145"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="147"/>
       <c r="H9" s="21" t="s">
         <v>160</v>
       </c>
@@ -8664,14 +8667,14 @@
       <c r="Q9" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="R9" s="167" t="s">
+      <c r="R9" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="S9" s="145"/>
-      <c r="T9" s="145"/>
-      <c r="U9" s="145"/>
-      <c r="V9" s="145"/>
-      <c r="W9" s="145"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="147"/>
+      <c r="U9" s="147"/>
+      <c r="V9" s="147"/>
+      <c r="W9" s="147"/>
       <c r="X9" s="21" t="s">
         <v>160</v>
       </c>
@@ -8702,14 +8705,14 @@
       <c r="AG9" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AH9" s="167" t="s">
+      <c r="AH9" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="AI9" s="145"/>
-      <c r="AJ9" s="145"/>
-      <c r="AK9" s="145"/>
-      <c r="AL9" s="145"/>
-      <c r="AM9" s="145"/>
+      <c r="AI9" s="147"/>
+      <c r="AJ9" s="147"/>
+      <c r="AK9" s="147"/>
+      <c r="AL9" s="147"/>
+      <c r="AM9" s="147"/>
       <c r="AN9" s="21" t="s">
         <v>160</v>
       </c>
@@ -8742,15 +8745,15 @@
       <c r="A10" s="22">
         <v>1</v>
       </c>
-      <c r="B10" s="163" t="str">
+      <c r="B10" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$3:$B$6,MATCH(1,Calc!$J$3:$J$6,0)),"?")</f>
         <v>Mexico</v>
       </c>
-      <c r="C10" s="145"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="145"/>
-      <c r="F10" s="145"/>
-      <c r="G10" s="145"/>
+      <c r="C10" s="147"/>
+      <c r="D10" s="147"/>
+      <c r="E10" s="147"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="147"/>
       <c r="H10" s="23">
         <f>IFERROR(INDEX(Calc!$H$3:$H$6,MATCH(1,Calc!$J$3:$J$6,0)),0)</f>
         <v>5</v>
@@ -8790,15 +8793,15 @@
       <c r="Q10" s="22">
         <v>1</v>
       </c>
-      <c r="R10" s="163" t="str">
+      <c r="R10" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$7:$B$10,MATCH(1,Calc!$J$7:$J$10,0)),"?")</f>
         <v>Canada</v>
       </c>
-      <c r="S10" s="145"/>
-      <c r="T10" s="145"/>
-      <c r="U10" s="145"/>
-      <c r="V10" s="145"/>
-      <c r="W10" s="145"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="147"/>
+      <c r="U10" s="147"/>
+      <c r="V10" s="147"/>
+      <c r="W10" s="147"/>
       <c r="X10" s="23">
         <f>IFERROR(INDEX(Calc!$H$7:$H$10,MATCH(1,Calc!$J$7:$J$10,0)),0)</f>
         <v>7</v>
@@ -8838,15 +8841,15 @@
       <c r="AG10" s="22">
         <v>1</v>
       </c>
-      <c r="AH10" s="163" t="str">
+      <c r="AH10" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$11:$B$14,MATCH(1,Calc!$J$11:$J$14,0)),"?")</f>
         <v>Brasil</v>
       </c>
-      <c r="AI10" s="145"/>
-      <c r="AJ10" s="145"/>
-      <c r="AK10" s="145"/>
-      <c r="AL10" s="145"/>
-      <c r="AM10" s="145"/>
+      <c r="AI10" s="147"/>
+      <c r="AJ10" s="147"/>
+      <c r="AK10" s="147"/>
+      <c r="AL10" s="147"/>
+      <c r="AM10" s="147"/>
       <c r="AN10" s="23">
         <f>IFERROR(INDEX(Calc!$H$11:$H$14,MATCH(1,Calc!$J$11:$J$14,0)),0)</f>
         <v>9</v>
@@ -8888,15 +8891,15 @@
       <c r="A11" s="24">
         <v>2</v>
       </c>
-      <c r="B11" s="152" t="str">
+      <c r="B11" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$3:$B$6,MATCH(2,Calc!$J$3:$J$6,0)),"?")</f>
         <v>Tchequia</v>
       </c>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145"/>
-      <c r="G11" s="145"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
       <c r="H11" s="25">
         <f>IFERROR(INDEX(Calc!$H$3:$H$6,MATCH(2,Calc!$J$3:$J$6,0)),0)</f>
         <v>5</v>
@@ -8936,15 +8939,15 @@
       <c r="Q11" s="24">
         <v>2</v>
       </c>
-      <c r="R11" s="152" t="str">
+      <c r="R11" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$7:$B$10,MATCH(2,Calc!$J$7:$J$10,0)),"?")</f>
         <v>Suica</v>
       </c>
-      <c r="S11" s="145"/>
-      <c r="T11" s="145"/>
-      <c r="U11" s="145"/>
-      <c r="V11" s="145"/>
-      <c r="W11" s="145"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="147"/>
+      <c r="U11" s="147"/>
+      <c r="V11" s="147"/>
+      <c r="W11" s="147"/>
       <c r="X11" s="25">
         <f>IFERROR(INDEX(Calc!$H$7:$H$10,MATCH(2,Calc!$J$7:$J$10,0)),0)</f>
         <v>5</v>
@@ -8984,15 +8987,15 @@
       <c r="AG11" s="24">
         <v>2</v>
       </c>
-      <c r="AH11" s="152" t="str">
+      <c r="AH11" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$11:$B$14,MATCH(2,Calc!$J$11:$J$14,0)),"?")</f>
         <v>Marrocos</v>
       </c>
-      <c r="AI11" s="145"/>
-      <c r="AJ11" s="145"/>
-      <c r="AK11" s="145"/>
-      <c r="AL11" s="145"/>
-      <c r="AM11" s="145"/>
+      <c r="AI11" s="147"/>
+      <c r="AJ11" s="147"/>
+      <c r="AK11" s="147"/>
+      <c r="AL11" s="147"/>
+      <c r="AM11" s="147"/>
       <c r="AN11" s="25">
         <f>IFERROR(INDEX(Calc!$H$11:$H$14,MATCH(2,Calc!$J$11:$J$14,0)),0)</f>
         <v>4</v>
@@ -9034,15 +9037,15 @@
       <c r="A12" s="26">
         <v>3</v>
       </c>
-      <c r="B12" s="165" t="str">
+      <c r="B12" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$3:$B$6,MATCH(3,Calc!$J$3:$J$6,0)),"?")</f>
         <v>Coreia do Sul</v>
       </c>
-      <c r="C12" s="145"/>
-      <c r="D12" s="145"/>
-      <c r="E12" s="145"/>
-      <c r="F12" s="145"/>
-      <c r="G12" s="145"/>
+      <c r="C12" s="147"/>
+      <c r="D12" s="147"/>
+      <c r="E12" s="147"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="147"/>
       <c r="H12" s="27">
         <f>IFERROR(INDEX(Calc!$H$3:$H$6,MATCH(3,Calc!$J$3:$J$6,0)),0)</f>
         <v>3</v>
@@ -9082,15 +9085,15 @@
       <c r="Q12" s="26">
         <v>3</v>
       </c>
-      <c r="R12" s="165" t="str">
+      <c r="R12" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$7:$B$10,MATCH(3,Calc!$J$7:$J$10,0)),"?")</f>
         <v>Bosnia e Herzegovina</v>
       </c>
-      <c r="S12" s="145"/>
-      <c r="T12" s="145"/>
-      <c r="U12" s="145"/>
-      <c r="V12" s="145"/>
-      <c r="W12" s="145"/>
+      <c r="S12" s="147"/>
+      <c r="T12" s="147"/>
+      <c r="U12" s="147"/>
+      <c r="V12" s="147"/>
+      <c r="W12" s="147"/>
       <c r="X12" s="27">
         <f>IFERROR(INDEX(Calc!$H$7:$H$10,MATCH(3,Calc!$J$7:$J$10,0)),0)</f>
         <v>4</v>
@@ -9130,15 +9133,15 @@
       <c r="AG12" s="26">
         <v>3</v>
       </c>
-      <c r="AH12" s="165" t="str">
+      <c r="AH12" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$11:$B$14,MATCH(3,Calc!$J$11:$J$14,0)),"?")</f>
         <v>Escocia</v>
       </c>
-      <c r="AI12" s="145"/>
-      <c r="AJ12" s="145"/>
-      <c r="AK12" s="145"/>
-      <c r="AL12" s="145"/>
-      <c r="AM12" s="145"/>
+      <c r="AI12" s="147"/>
+      <c r="AJ12" s="147"/>
+      <c r="AK12" s="147"/>
+      <c r="AL12" s="147"/>
+      <c r="AM12" s="147"/>
       <c r="AN12" s="27">
         <f>IFERROR(INDEX(Calc!$H$11:$H$14,MATCH(3,Calc!$J$11:$J$14,0)),0)</f>
         <v>4</v>
@@ -9180,15 +9183,15 @@
       <c r="A13" s="28">
         <v>4</v>
       </c>
-      <c r="B13" s="164" t="str">
+      <c r="B13" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$3:$B$6,MATCH(4,Calc!$J$3:$J$6,0)),"?")</f>
         <v>Africa do Sul</v>
       </c>
-      <c r="C13" s="145"/>
-      <c r="D13" s="145"/>
-      <c r="E13" s="145"/>
-      <c r="F13" s="145"/>
-      <c r="G13" s="145"/>
+      <c r="C13" s="147"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
       <c r="H13" s="29">
         <f>IFERROR(INDEX(Calc!$H$3:$H$6,MATCH(4,Calc!$J$3:$J$6,0)),0)</f>
         <v>1</v>
@@ -9228,15 +9231,15 @@
       <c r="Q13" s="28">
         <v>4</v>
       </c>
-      <c r="R13" s="164" t="str">
+      <c r="R13" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$7:$B$10,MATCH(4,Calc!$J$7:$J$10,0)),"?")</f>
         <v>Qatar</v>
       </c>
-      <c r="S13" s="145"/>
-      <c r="T13" s="145"/>
-      <c r="U13" s="145"/>
-      <c r="V13" s="145"/>
-      <c r="W13" s="145"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="147"/>
+      <c r="U13" s="147"/>
+      <c r="V13" s="147"/>
+      <c r="W13" s="147"/>
       <c r="X13" s="29">
         <f>IFERROR(INDEX(Calc!$H$7:$H$10,MATCH(4,Calc!$J$7:$J$10,0)),0)</f>
         <v>0</v>
@@ -9276,15 +9279,15 @@
       <c r="AG13" s="28">
         <v>4</v>
       </c>
-      <c r="AH13" s="164" t="str">
+      <c r="AH13" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$11:$B$14,MATCH(4,Calc!$J$11:$J$14,0)),"?")</f>
         <v>Haiti</v>
       </c>
-      <c r="AI13" s="145"/>
-      <c r="AJ13" s="145"/>
-      <c r="AK13" s="145"/>
-      <c r="AL13" s="145"/>
-      <c r="AM13" s="145"/>
+      <c r="AI13" s="147"/>
+      <c r="AJ13" s="147"/>
+      <c r="AK13" s="147"/>
+      <c r="AL13" s="147"/>
+      <c r="AM13" s="147"/>
       <c r="AN13" s="29">
         <f>IFERROR(INDEX(Calc!$H$11:$H$14,MATCH(4,Calc!$J$11:$J$14,0)),0)</f>
         <v>0</v>
@@ -9322,71 +9325,71 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:145" ht="21.95" customHeight="1">
-      <c r="A15" s="162" t="s">
+    <row r="15" spans="1:145" ht="21.9" customHeight="1">
+      <c r="A15" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="145"/>
-      <c r="C15" s="145"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="145"/>
-      <c r="F15" s="145"/>
-      <c r="G15" s="145"/>
-      <c r="H15" s="145"/>
-      <c r="I15" s="145"/>
-      <c r="J15" s="145"/>
-      <c r="K15" s="145"/>
-      <c r="L15" s="145"/>
-      <c r="M15" s="145"/>
-      <c r="N15" s="145"/>
-      <c r="O15" s="145"/>
-      <c r="Q15" s="179" t="s">
+      <c r="B15" s="147"/>
+      <c r="C15" s="147"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="147"/>
+      <c r="F15" s="147"/>
+      <c r="G15" s="147"/>
+      <c r="H15" s="147"/>
+      <c r="I15" s="147"/>
+      <c r="J15" s="147"/>
+      <c r="K15" s="147"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="147"/>
+      <c r="N15" s="147"/>
+      <c r="O15" s="147"/>
+      <c r="Q15" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="R15" s="145"/>
-      <c r="S15" s="145"/>
-      <c r="T15" s="145"/>
-      <c r="U15" s="145"/>
-      <c r="V15" s="145"/>
-      <c r="W15" s="145"/>
-      <c r="X15" s="145"/>
-      <c r="Y15" s="145"/>
-      <c r="Z15" s="145"/>
-      <c r="AA15" s="145"/>
-      <c r="AB15" s="145"/>
-      <c r="AC15" s="145"/>
-      <c r="AD15" s="145"/>
-      <c r="AE15" s="145"/>
-      <c r="AG15" s="155" t="s">
+      <c r="R15" s="147"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="147"/>
+      <c r="U15" s="147"/>
+      <c r="V15" s="147"/>
+      <c r="W15" s="147"/>
+      <c r="X15" s="147"/>
+      <c r="Y15" s="147"/>
+      <c r="Z15" s="147"/>
+      <c r="AA15" s="147"/>
+      <c r="AB15" s="147"/>
+      <c r="AC15" s="147"/>
+      <c r="AD15" s="147"/>
+      <c r="AE15" s="147"/>
+      <c r="AG15" s="205" t="s">
         <v>171</v>
       </c>
-      <c r="AH15" s="145"/>
-      <c r="AI15" s="145"/>
-      <c r="AJ15" s="145"/>
-      <c r="AK15" s="145"/>
-      <c r="AL15" s="145"/>
-      <c r="AM15" s="145"/>
-      <c r="AN15" s="145"/>
-      <c r="AO15" s="145"/>
-      <c r="AP15" s="145"/>
-      <c r="AQ15" s="145"/>
-      <c r="AR15" s="145"/>
-      <c r="AS15" s="145"/>
-      <c r="AT15" s="145"/>
-      <c r="AU15" s="145"/>
+      <c r="AH15" s="147"/>
+      <c r="AI15" s="147"/>
+      <c r="AJ15" s="147"/>
+      <c r="AK15" s="147"/>
+      <c r="AL15" s="147"/>
+      <c r="AM15" s="147"/>
+      <c r="AN15" s="147"/>
+      <c r="AO15" s="147"/>
+      <c r="AP15" s="147"/>
+      <c r="AQ15" s="147"/>
+      <c r="AR15" s="147"/>
+      <c r="AS15" s="147"/>
+      <c r="AT15" s="147"/>
+      <c r="AU15" s="147"/>
     </row>
     <row r="16" spans="1:145" ht="18" customHeight="1">
       <c r="A16" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="167" t="s">
+      <c r="B16" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="C16" s="145"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="145"/>
-      <c r="F16" s="145"/>
-      <c r="G16" s="145"/>
+      <c r="C16" s="147"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="147"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="147"/>
       <c r="H16" s="21" t="s">
         <v>160</v>
       </c>
@@ -9417,14 +9420,14 @@
       <c r="Q16" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="R16" s="167" t="s">
+      <c r="R16" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="S16" s="145"/>
-      <c r="T16" s="145"/>
-      <c r="U16" s="145"/>
-      <c r="V16" s="145"/>
-      <c r="W16" s="145"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="147"/>
+      <c r="U16" s="147"/>
+      <c r="V16" s="147"/>
+      <c r="W16" s="147"/>
       <c r="X16" s="21" t="s">
         <v>160</v>
       </c>
@@ -9455,14 +9458,14 @@
       <c r="AG16" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AH16" s="167" t="s">
+      <c r="AH16" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="AI16" s="145"/>
-      <c r="AJ16" s="145"/>
-      <c r="AK16" s="145"/>
-      <c r="AL16" s="145"/>
-      <c r="AM16" s="145"/>
+      <c r="AI16" s="147"/>
+      <c r="AJ16" s="147"/>
+      <c r="AK16" s="147"/>
+      <c r="AL16" s="147"/>
+      <c r="AM16" s="147"/>
       <c r="AN16" s="21" t="s">
         <v>160</v>
       </c>
@@ -9495,15 +9498,15 @@
       <c r="A17" s="22">
         <v>1</v>
       </c>
-      <c r="B17" s="163" t="str">
+      <c r="B17" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$15:$B$18,MATCH(1,Calc!$J$15:$J$18,0)),"?")</f>
         <v>Estados Unidos</v>
       </c>
-      <c r="C17" s="145"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="145"/>
-      <c r="G17" s="145"/>
+      <c r="C17" s="147"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="147"/>
       <c r="H17" s="23">
         <f>IFERROR(INDEX(Calc!$H$15:$H$18,MATCH(1,Calc!$J$15:$J$18,0)),0)</f>
         <v>7</v>
@@ -9543,15 +9546,15 @@
       <c r="Q17" s="22">
         <v>1</v>
       </c>
-      <c r="R17" s="163" t="str">
+      <c r="R17" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$19:$B$22,MATCH(1,Calc!$J$19:$J$22,0)),"?")</f>
         <v>Alemanha</v>
       </c>
-      <c r="S17" s="145"/>
-      <c r="T17" s="145"/>
-      <c r="U17" s="145"/>
-      <c r="V17" s="145"/>
-      <c r="W17" s="145"/>
+      <c r="S17" s="147"/>
+      <c r="T17" s="147"/>
+      <c r="U17" s="147"/>
+      <c r="V17" s="147"/>
+      <c r="W17" s="147"/>
       <c r="X17" s="23">
         <f>IFERROR(INDEX(Calc!$H$19:$H$22,MATCH(1,Calc!$J$19:$J$22,0)),0)</f>
         <v>9</v>
@@ -9591,15 +9594,15 @@
       <c r="AG17" s="22">
         <v>1</v>
       </c>
-      <c r="AH17" s="163" t="str">
+      <c r="AH17" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$23:$B$26,MATCH(1,Calc!$J$23:$J$26,0)),"?")</f>
         <v>Holanda</v>
       </c>
-      <c r="AI17" s="145"/>
-      <c r="AJ17" s="145"/>
-      <c r="AK17" s="145"/>
-      <c r="AL17" s="145"/>
-      <c r="AM17" s="145"/>
+      <c r="AI17" s="147"/>
+      <c r="AJ17" s="147"/>
+      <c r="AK17" s="147"/>
+      <c r="AL17" s="147"/>
+      <c r="AM17" s="147"/>
       <c r="AN17" s="23">
         <f>IFERROR(INDEX(Calc!$H$23:$H$26,MATCH(1,Calc!$J$23:$J$26,0)),0)</f>
         <v>9</v>
@@ -9641,15 +9644,15 @@
       <c r="A18" s="24">
         <v>2</v>
       </c>
-      <c r="B18" s="152" t="str">
+      <c r="B18" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$15:$B$18,MATCH(2,Calc!$J$15:$J$18,0)),"?")</f>
         <v>Australia</v>
       </c>
-      <c r="C18" s="145"/>
-      <c r="D18" s="145"/>
-      <c r="E18" s="145"/>
-      <c r="F18" s="145"/>
-      <c r="G18" s="145"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
       <c r="H18" s="25">
         <f>IFERROR(INDEX(Calc!$H$15:$H$18,MATCH(2,Calc!$J$15:$J$18,0)),0)</f>
         <v>4</v>
@@ -9689,15 +9692,15 @@
       <c r="Q18" s="24">
         <v>2</v>
       </c>
-      <c r="R18" s="152" t="str">
+      <c r="R18" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$19:$B$22,MATCH(2,Calc!$J$19:$J$22,0)),"?")</f>
         <v>Equador</v>
       </c>
-      <c r="S18" s="145"/>
-      <c r="T18" s="145"/>
-      <c r="U18" s="145"/>
-      <c r="V18" s="145"/>
-      <c r="W18" s="145"/>
+      <c r="S18" s="147"/>
+      <c r="T18" s="147"/>
+      <c r="U18" s="147"/>
+      <c r="V18" s="147"/>
+      <c r="W18" s="147"/>
       <c r="X18" s="25">
         <f>IFERROR(INDEX(Calc!$H$19:$H$22,MATCH(2,Calc!$J$19:$J$22,0)),0)</f>
         <v>6</v>
@@ -9737,15 +9740,15 @@
       <c r="AG18" s="24">
         <v>2</v>
       </c>
-      <c r="AH18" s="152" t="str">
+      <c r="AH18" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$23:$B$26,MATCH(2,Calc!$J$23:$J$26,0)),"?")</f>
         <v>Japao</v>
       </c>
-      <c r="AI18" s="145"/>
-      <c r="AJ18" s="145"/>
-      <c r="AK18" s="145"/>
-      <c r="AL18" s="145"/>
-      <c r="AM18" s="145"/>
+      <c r="AI18" s="147"/>
+      <c r="AJ18" s="147"/>
+      <c r="AK18" s="147"/>
+      <c r="AL18" s="147"/>
+      <c r="AM18" s="147"/>
       <c r="AN18" s="25">
         <f>IFERROR(INDEX(Calc!$H$23:$H$26,MATCH(2,Calc!$J$23:$J$26,0)),0)</f>
         <v>4</v>
@@ -9787,15 +9790,15 @@
       <c r="A19" s="26">
         <v>3</v>
       </c>
-      <c r="B19" s="165" t="str">
+      <c r="B19" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$15:$B$18,MATCH(3,Calc!$J$15:$J$18,0)),"?")</f>
         <v>Turquia</v>
       </c>
-      <c r="C19" s="145"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="145"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="145"/>
+      <c r="C19" s="147"/>
+      <c r="D19" s="147"/>
+      <c r="E19" s="147"/>
+      <c r="F19" s="147"/>
+      <c r="G19" s="147"/>
       <c r="H19" s="27">
         <f>IFERROR(INDEX(Calc!$H$15:$H$18,MATCH(3,Calc!$J$15:$J$18,0)),0)</f>
         <v>4</v>
@@ -9835,15 +9838,15 @@
       <c r="Q19" s="26">
         <v>3</v>
       </c>
-      <c r="R19" s="165" t="str">
+      <c r="R19" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$19:$B$22,MATCH(3,Calc!$J$19:$J$22,0)),"?")</f>
         <v>Curacao</v>
       </c>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
-      <c r="U19" s="145"/>
-      <c r="V19" s="145"/>
-      <c r="W19" s="145"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="147"/>
+      <c r="U19" s="147"/>
+      <c r="V19" s="147"/>
+      <c r="W19" s="147"/>
       <c r="X19" s="27">
         <f>IFERROR(INDEX(Calc!$H$19:$H$22,MATCH(3,Calc!$J$19:$J$22,0)),0)</f>
         <v>1</v>
@@ -9883,15 +9886,15 @@
       <c r="AG19" s="26">
         <v>3</v>
       </c>
-      <c r="AH19" s="165" t="str">
+      <c r="AH19" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$23:$B$26,MATCH(3,Calc!$J$23:$J$26,0)),"?")</f>
         <v>Suecia</v>
       </c>
-      <c r="AI19" s="145"/>
-      <c r="AJ19" s="145"/>
-      <c r="AK19" s="145"/>
-      <c r="AL19" s="145"/>
-      <c r="AM19" s="145"/>
+      <c r="AI19" s="147"/>
+      <c r="AJ19" s="147"/>
+      <c r="AK19" s="147"/>
+      <c r="AL19" s="147"/>
+      <c r="AM19" s="147"/>
       <c r="AN19" s="27">
         <f>IFERROR(INDEX(Calc!$H$23:$H$26,MATCH(3,Calc!$J$23:$J$26,0)),0)</f>
         <v>2</v>
@@ -9933,15 +9936,15 @@
       <c r="A20" s="28">
         <v>4</v>
       </c>
-      <c r="B20" s="164" t="str">
+      <c r="B20" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$15:$B$18,MATCH(4,Calc!$J$15:$J$18,0)),"?")</f>
         <v>Paraguai</v>
       </c>
-      <c r="C20" s="145"/>
-      <c r="D20" s="145"/>
-      <c r="E20" s="145"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="145"/>
+      <c r="C20" s="147"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="147"/>
+      <c r="G20" s="147"/>
       <c r="H20" s="29">
         <f>IFERROR(INDEX(Calc!$H$15:$H$18,MATCH(4,Calc!$J$15:$J$18,0)),0)</f>
         <v>1</v>
@@ -9981,15 +9984,15 @@
       <c r="Q20" s="28">
         <v>4</v>
       </c>
-      <c r="R20" s="164" t="str">
+      <c r="R20" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$19:$B$22,MATCH(4,Calc!$J$19:$J$22,0)),"?")</f>
         <v>Costa do Marfim</v>
       </c>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
-      <c r="U20" s="145"/>
-      <c r="V20" s="145"/>
-      <c r="W20" s="145"/>
+      <c r="S20" s="147"/>
+      <c r="T20" s="147"/>
+      <c r="U20" s="147"/>
+      <c r="V20" s="147"/>
+      <c r="W20" s="147"/>
       <c r="X20" s="29">
         <f>IFERROR(INDEX(Calc!$H$19:$H$22,MATCH(4,Calc!$J$19:$J$22,0)),0)</f>
         <v>1</v>
@@ -10029,15 +10032,15 @@
       <c r="AG20" s="28">
         <v>4</v>
       </c>
-      <c r="AH20" s="164" t="str">
+      <c r="AH20" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$23:$B$26,MATCH(4,Calc!$J$23:$J$26,0)),"?")</f>
         <v>Tunisia</v>
       </c>
-      <c r="AI20" s="145"/>
-      <c r="AJ20" s="145"/>
-      <c r="AK20" s="145"/>
-      <c r="AL20" s="145"/>
-      <c r="AM20" s="145"/>
+      <c r="AI20" s="147"/>
+      <c r="AJ20" s="147"/>
+      <c r="AK20" s="147"/>
+      <c r="AL20" s="147"/>
+      <c r="AM20" s="147"/>
       <c r="AN20" s="29">
         <f>IFERROR(INDEX(Calc!$H$23:$H$26,MATCH(4,Calc!$J$23:$J$26,0)),0)</f>
         <v>1</v>
@@ -10075,71 +10078,71 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:48" ht="21.95" customHeight="1">
-      <c r="A22" s="175" t="s">
+    <row r="22" spans="1:48" ht="21.9" customHeight="1">
+      <c r="A22" s="193" t="s">
         <v>172</v>
       </c>
-      <c r="B22" s="145"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="145"/>
-      <c r="E22" s="145"/>
-      <c r="F22" s="145"/>
-      <c r="G22" s="145"/>
-      <c r="H22" s="145"/>
-      <c r="I22" s="145"/>
-      <c r="J22" s="145"/>
-      <c r="K22" s="145"/>
-      <c r="L22" s="145"/>
-      <c r="M22" s="145"/>
-      <c r="N22" s="145"/>
-      <c r="O22" s="145"/>
-      <c r="Q22" s="174" t="s">
+      <c r="B22" s="147"/>
+      <c r="C22" s="147"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="147"/>
+      <c r="F22" s="147"/>
+      <c r="G22" s="147"/>
+      <c r="H22" s="147"/>
+      <c r="I22" s="147"/>
+      <c r="J22" s="147"/>
+      <c r="K22" s="147"/>
+      <c r="L22" s="147"/>
+      <c r="M22" s="147"/>
+      <c r="N22" s="147"/>
+      <c r="O22" s="147"/>
+      <c r="Q22" s="197" t="s">
         <v>173</v>
       </c>
-      <c r="R22" s="145"/>
-      <c r="S22" s="145"/>
-      <c r="T22" s="145"/>
-      <c r="U22" s="145"/>
-      <c r="V22" s="145"/>
-      <c r="W22" s="145"/>
-      <c r="X22" s="145"/>
-      <c r="Y22" s="145"/>
-      <c r="Z22" s="145"/>
-      <c r="AA22" s="145"/>
-      <c r="AB22" s="145"/>
-      <c r="AC22" s="145"/>
-      <c r="AD22" s="145"/>
-      <c r="AE22" s="145"/>
-      <c r="AG22" s="169" t="s">
+      <c r="R22" s="147"/>
+      <c r="S22" s="147"/>
+      <c r="T22" s="147"/>
+      <c r="U22" s="147"/>
+      <c r="V22" s="147"/>
+      <c r="W22" s="147"/>
+      <c r="X22" s="147"/>
+      <c r="Y22" s="147"/>
+      <c r="Z22" s="147"/>
+      <c r="AA22" s="147"/>
+      <c r="AB22" s="147"/>
+      <c r="AC22" s="147"/>
+      <c r="AD22" s="147"/>
+      <c r="AE22" s="147"/>
+      <c r="AG22" s="203" t="s">
         <v>174</v>
       </c>
-      <c r="AH22" s="145"/>
-      <c r="AI22" s="145"/>
-      <c r="AJ22" s="145"/>
-      <c r="AK22" s="145"/>
-      <c r="AL22" s="145"/>
-      <c r="AM22" s="145"/>
-      <c r="AN22" s="145"/>
-      <c r="AO22" s="145"/>
-      <c r="AP22" s="145"/>
-      <c r="AQ22" s="145"/>
-      <c r="AR22" s="145"/>
-      <c r="AS22" s="145"/>
-      <c r="AT22" s="145"/>
-      <c r="AU22" s="145"/>
+      <c r="AH22" s="147"/>
+      <c r="AI22" s="147"/>
+      <c r="AJ22" s="147"/>
+      <c r="AK22" s="147"/>
+      <c r="AL22" s="147"/>
+      <c r="AM22" s="147"/>
+      <c r="AN22" s="147"/>
+      <c r="AO22" s="147"/>
+      <c r="AP22" s="147"/>
+      <c r="AQ22" s="147"/>
+      <c r="AR22" s="147"/>
+      <c r="AS22" s="147"/>
+      <c r="AT22" s="147"/>
+      <c r="AU22" s="147"/>
     </row>
     <row r="23" spans="1:48" ht="18" customHeight="1">
       <c r="A23" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="167" t="s">
+      <c r="B23" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="145"/>
+      <c r="C23" s="147"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="147"/>
+      <c r="G23" s="147"/>
       <c r="H23" s="21" t="s">
         <v>160</v>
       </c>
@@ -10170,14 +10173,14 @@
       <c r="Q23" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="R23" s="167" t="s">
+      <c r="R23" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="S23" s="145"/>
-      <c r="T23" s="145"/>
-      <c r="U23" s="145"/>
-      <c r="V23" s="145"/>
-      <c r="W23" s="145"/>
+      <c r="S23" s="147"/>
+      <c r="T23" s="147"/>
+      <c r="U23" s="147"/>
+      <c r="V23" s="147"/>
+      <c r="W23" s="147"/>
       <c r="X23" s="21" t="s">
         <v>160</v>
       </c>
@@ -10208,14 +10211,14 @@
       <c r="AG23" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AH23" s="167" t="s">
+      <c r="AH23" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="AI23" s="145"/>
-      <c r="AJ23" s="145"/>
-      <c r="AK23" s="145"/>
-      <c r="AL23" s="145"/>
-      <c r="AM23" s="145"/>
+      <c r="AI23" s="147"/>
+      <c r="AJ23" s="147"/>
+      <c r="AK23" s="147"/>
+      <c r="AL23" s="147"/>
+      <c r="AM23" s="147"/>
       <c r="AN23" s="21" t="s">
         <v>160</v>
       </c>
@@ -10248,15 +10251,15 @@
       <c r="A24" s="22">
         <v>1</v>
       </c>
-      <c r="B24" s="163" t="str">
+      <c r="B24" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$27:$B$30,MATCH(1,Calc!$J$27:$J$30,0)),"?")</f>
         <v>Belgica</v>
       </c>
-      <c r="C24" s="145"/>
-      <c r="D24" s="145"/>
-      <c r="E24" s="145"/>
-      <c r="F24" s="145"/>
-      <c r="G24" s="145"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="147"/>
+      <c r="G24" s="147"/>
       <c r="H24" s="23">
         <f>IFERROR(INDEX(Calc!$H$27:$H$30,MATCH(1,Calc!$J$27:$J$30,0)),0)</f>
         <v>7</v>
@@ -10296,15 +10299,15 @@
       <c r="Q24" s="22">
         <v>1</v>
       </c>
-      <c r="R24" s="163" t="str">
+      <c r="R24" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$31:$B$34,MATCH(1,Calc!$J$31:$J$34,0)),"?")</f>
         <v>Espanha</v>
       </c>
-      <c r="S24" s="145"/>
-      <c r="T24" s="145"/>
-      <c r="U24" s="145"/>
-      <c r="V24" s="145"/>
-      <c r="W24" s="145"/>
+      <c r="S24" s="147"/>
+      <c r="T24" s="147"/>
+      <c r="U24" s="147"/>
+      <c r="V24" s="147"/>
+      <c r="W24" s="147"/>
       <c r="X24" s="23">
         <f>IFERROR(INDEX(Calc!$H$31:$H$34,MATCH(1,Calc!$J$31:$J$34,0)),0)</f>
         <v>9</v>
@@ -10344,15 +10347,15 @@
       <c r="AG24" s="22">
         <v>1</v>
       </c>
-      <c r="AH24" s="163" t="str">
+      <c r="AH24" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$35:$B$38,MATCH(1,Calc!$J$35:$J$38,0)),"?")</f>
         <v>Franca</v>
       </c>
-      <c r="AI24" s="145"/>
-      <c r="AJ24" s="145"/>
-      <c r="AK24" s="145"/>
-      <c r="AL24" s="145"/>
-      <c r="AM24" s="145"/>
+      <c r="AI24" s="147"/>
+      <c r="AJ24" s="147"/>
+      <c r="AK24" s="147"/>
+      <c r="AL24" s="147"/>
+      <c r="AM24" s="147"/>
       <c r="AN24" s="23">
         <f>IFERROR(INDEX(Calc!$H$35:$H$38,MATCH(1,Calc!$J$35:$J$38,0)),0)</f>
         <v>9</v>
@@ -10394,15 +10397,15 @@
       <c r="A25" s="24">
         <v>2</v>
       </c>
-      <c r="B25" s="152" t="str">
+      <c r="B25" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$27:$B$30,MATCH(2,Calc!$J$27:$J$30,0)),"?")</f>
         <v>Egito</v>
       </c>
-      <c r="C25" s="145"/>
-      <c r="D25" s="145"/>
-      <c r="E25" s="145"/>
-      <c r="F25" s="145"/>
-      <c r="G25" s="145"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="147"/>
+      <c r="F25" s="147"/>
+      <c r="G25" s="147"/>
       <c r="H25" s="25">
         <f>IFERROR(INDEX(Calc!$H$27:$H$30,MATCH(2,Calc!$J$27:$J$30,0)),0)</f>
         <v>7</v>
@@ -10442,15 +10445,15 @@
       <c r="Q25" s="24">
         <v>2</v>
       </c>
-      <c r="R25" s="152" t="str">
+      <c r="R25" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$31:$B$34,MATCH(2,Calc!$J$31:$J$34,0)),"?")</f>
         <v>Uruguai</v>
       </c>
-      <c r="S25" s="145"/>
-      <c r="T25" s="145"/>
-      <c r="U25" s="145"/>
-      <c r="V25" s="145"/>
-      <c r="W25" s="145"/>
+      <c r="S25" s="147"/>
+      <c r="T25" s="147"/>
+      <c r="U25" s="147"/>
+      <c r="V25" s="147"/>
+      <c r="W25" s="147"/>
       <c r="X25" s="25">
         <f>IFERROR(INDEX(Calc!$H$31:$H$34,MATCH(2,Calc!$J$31:$J$34,0)),0)</f>
         <v>6</v>
@@ -10490,15 +10493,15 @@
       <c r="AG25" s="24">
         <v>2</v>
       </c>
-      <c r="AH25" s="152" t="str">
+      <c r="AH25" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$35:$B$38,MATCH(2,Calc!$J$35:$J$38,0)),"?")</f>
         <v>Noruega</v>
       </c>
-      <c r="AI25" s="145"/>
-      <c r="AJ25" s="145"/>
-      <c r="AK25" s="145"/>
-      <c r="AL25" s="145"/>
-      <c r="AM25" s="145"/>
+      <c r="AI25" s="147"/>
+      <c r="AJ25" s="147"/>
+      <c r="AK25" s="147"/>
+      <c r="AL25" s="147"/>
+      <c r="AM25" s="147"/>
       <c r="AN25" s="25">
         <f>IFERROR(INDEX(Calc!$H$35:$H$38,MATCH(2,Calc!$J$35:$J$38,0)),0)</f>
         <v>6</v>
@@ -10540,15 +10543,15 @@
       <c r="A26" s="26">
         <v>3</v>
       </c>
-      <c r="B26" s="165" t="str">
+      <c r="B26" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$27:$B$30,MATCH(3,Calc!$J$27:$J$30,0)),"?")</f>
         <v>Nova Zelandia</v>
       </c>
-      <c r="C26" s="145"/>
-      <c r="D26" s="145"/>
-      <c r="E26" s="145"/>
-      <c r="F26" s="145"/>
-      <c r="G26" s="145"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="147"/>
       <c r="H26" s="27">
         <f>IFERROR(INDEX(Calc!$H$27:$H$30,MATCH(3,Calc!$J$27:$J$30,0)),0)</f>
         <v>1</v>
@@ -10588,15 +10591,15 @@
       <c r="Q26" s="26">
         <v>3</v>
       </c>
-      <c r="R26" s="165" t="str">
+      <c r="R26" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$31:$B$34,MATCH(3,Calc!$J$31:$J$34,0)),"?")</f>
         <v>Arabia Saudita</v>
       </c>
-      <c r="S26" s="145"/>
-      <c r="T26" s="145"/>
-      <c r="U26" s="145"/>
-      <c r="V26" s="145"/>
-      <c r="W26" s="145"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="147"/>
+      <c r="U26" s="147"/>
+      <c r="V26" s="147"/>
+      <c r="W26" s="147"/>
       <c r="X26" s="27">
         <f>IFERROR(INDEX(Calc!$H$31:$H$34,MATCH(3,Calc!$J$31:$J$34,0)),0)</f>
         <v>1</v>
@@ -10636,15 +10639,15 @@
       <c r="AG26" s="26">
         <v>3</v>
       </c>
-      <c r="AH26" s="165" t="str">
+      <c r="AH26" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$35:$B$38,MATCH(3,Calc!$J$35:$J$38,0)),"?")</f>
         <v>Senegal</v>
       </c>
-      <c r="AI26" s="145"/>
-      <c r="AJ26" s="145"/>
-      <c r="AK26" s="145"/>
-      <c r="AL26" s="145"/>
-      <c r="AM26" s="145"/>
+      <c r="AI26" s="147"/>
+      <c r="AJ26" s="147"/>
+      <c r="AK26" s="147"/>
+      <c r="AL26" s="147"/>
+      <c r="AM26" s="147"/>
       <c r="AN26" s="27">
         <f>IFERROR(INDEX(Calc!$H$35:$H$38,MATCH(3,Calc!$J$35:$J$38,0)),0)</f>
         <v>1</v>
@@ -10686,15 +10689,15 @@
       <c r="A27" s="28">
         <v>4</v>
       </c>
-      <c r="B27" s="164" t="str">
+      <c r="B27" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$27:$B$30,MATCH(4,Calc!$J$27:$J$30,0)),"?")</f>
         <v>Ira</v>
       </c>
-      <c r="C27" s="145"/>
-      <c r="D27" s="145"/>
-      <c r="E27" s="145"/>
-      <c r="F27" s="145"/>
-      <c r="G27" s="145"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="147"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="147"/>
       <c r="H27" s="29">
         <f>IFERROR(INDEX(Calc!$H$27:$H$30,MATCH(4,Calc!$J$27:$J$30,0)),0)</f>
         <v>1</v>
@@ -10734,15 +10737,15 @@
       <c r="Q27" s="28">
         <v>4</v>
       </c>
-      <c r="R27" s="164" t="str">
+      <c r="R27" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$31:$B$34,MATCH(4,Calc!$J$31:$J$34,0)),"?")</f>
         <v>Cabo Verde</v>
       </c>
-      <c r="S27" s="145"/>
-      <c r="T27" s="145"/>
-      <c r="U27" s="145"/>
-      <c r="V27" s="145"/>
-      <c r="W27" s="145"/>
+      <c r="S27" s="147"/>
+      <c r="T27" s="147"/>
+      <c r="U27" s="147"/>
+      <c r="V27" s="147"/>
+      <c r="W27" s="147"/>
       <c r="X27" s="29">
         <f>IFERROR(INDEX(Calc!$H$31:$H$34,MATCH(4,Calc!$J$31:$J$34,0)),0)</f>
         <v>1</v>
@@ -10782,15 +10785,15 @@
       <c r="AG27" s="28">
         <v>4</v>
       </c>
-      <c r="AH27" s="164" t="str">
+      <c r="AH27" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$35:$B$38,MATCH(4,Calc!$J$35:$J$38,0)),"?")</f>
         <v>Iraque</v>
       </c>
-      <c r="AI27" s="145"/>
-      <c r="AJ27" s="145"/>
-      <c r="AK27" s="145"/>
-      <c r="AL27" s="145"/>
-      <c r="AM27" s="145"/>
+      <c r="AI27" s="147"/>
+      <c r="AJ27" s="147"/>
+      <c r="AK27" s="147"/>
+      <c r="AL27" s="147"/>
+      <c r="AM27" s="147"/>
       <c r="AN27" s="29">
         <f>IFERROR(INDEX(Calc!$H$35:$H$38,MATCH(4,Calc!$J$35:$J$38,0)),0)</f>
         <v>1</v>
@@ -10828,71 +10831,71 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:48" ht="21.95" customHeight="1">
-      <c r="A29" s="176" t="s">
+    <row r="29" spans="1:48" ht="21.9" customHeight="1">
+      <c r="A29" s="194" t="s">
         <v>175</v>
       </c>
-      <c r="B29" s="145"/>
-      <c r="C29" s="145"/>
-      <c r="D29" s="145"/>
-      <c r="E29" s="145"/>
-      <c r="F29" s="145"/>
-      <c r="G29" s="145"/>
-      <c r="H29" s="145"/>
-      <c r="I29" s="145"/>
-      <c r="J29" s="145"/>
-      <c r="K29" s="145"/>
-      <c r="L29" s="145"/>
-      <c r="M29" s="145"/>
-      <c r="N29" s="145"/>
-      <c r="O29" s="145"/>
-      <c r="Q29" s="173" t="s">
+      <c r="B29" s="147"/>
+      <c r="C29" s="147"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="147"/>
+      <c r="F29" s="147"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="147"/>
+      <c r="I29" s="147"/>
+      <c r="J29" s="147"/>
+      <c r="K29" s="147"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="147"/>
+      <c r="N29" s="147"/>
+      <c r="O29" s="147"/>
+      <c r="Q29" s="196" t="s">
         <v>176</v>
       </c>
-      <c r="R29" s="145"/>
-      <c r="S29" s="145"/>
-      <c r="T29" s="145"/>
-      <c r="U29" s="145"/>
-      <c r="V29" s="145"/>
-      <c r="W29" s="145"/>
-      <c r="X29" s="145"/>
-      <c r="Y29" s="145"/>
-      <c r="Z29" s="145"/>
-      <c r="AA29" s="145"/>
-      <c r="AB29" s="145"/>
-      <c r="AC29" s="145"/>
-      <c r="AD29" s="145"/>
-      <c r="AE29" s="145"/>
-      <c r="AG29" s="168" t="s">
+      <c r="R29" s="147"/>
+      <c r="S29" s="147"/>
+      <c r="T29" s="147"/>
+      <c r="U29" s="147"/>
+      <c r="V29" s="147"/>
+      <c r="W29" s="147"/>
+      <c r="X29" s="147"/>
+      <c r="Y29" s="147"/>
+      <c r="Z29" s="147"/>
+      <c r="AA29" s="147"/>
+      <c r="AB29" s="147"/>
+      <c r="AC29" s="147"/>
+      <c r="AD29" s="147"/>
+      <c r="AE29" s="147"/>
+      <c r="AG29" s="202" t="s">
         <v>177</v>
       </c>
-      <c r="AH29" s="145"/>
-      <c r="AI29" s="145"/>
-      <c r="AJ29" s="145"/>
-      <c r="AK29" s="145"/>
-      <c r="AL29" s="145"/>
-      <c r="AM29" s="145"/>
-      <c r="AN29" s="145"/>
-      <c r="AO29" s="145"/>
-      <c r="AP29" s="145"/>
-      <c r="AQ29" s="145"/>
-      <c r="AR29" s="145"/>
-      <c r="AS29" s="145"/>
-      <c r="AT29" s="145"/>
-      <c r="AU29" s="145"/>
+      <c r="AH29" s="147"/>
+      <c r="AI29" s="147"/>
+      <c r="AJ29" s="147"/>
+      <c r="AK29" s="147"/>
+      <c r="AL29" s="147"/>
+      <c r="AM29" s="147"/>
+      <c r="AN29" s="147"/>
+      <c r="AO29" s="147"/>
+      <c r="AP29" s="147"/>
+      <c r="AQ29" s="147"/>
+      <c r="AR29" s="147"/>
+      <c r="AS29" s="147"/>
+      <c r="AT29" s="147"/>
+      <c r="AU29" s="147"/>
     </row>
     <row r="30" spans="1:48" ht="18" customHeight="1">
       <c r="A30" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B30" s="167" t="s">
+      <c r="B30" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="C30" s="145"/>
-      <c r="D30" s="145"/>
-      <c r="E30" s="145"/>
-      <c r="F30" s="145"/>
-      <c r="G30" s="145"/>
+      <c r="C30" s="147"/>
+      <c r="D30" s="147"/>
+      <c r="E30" s="147"/>
+      <c r="F30" s="147"/>
+      <c r="G30" s="147"/>
       <c r="H30" s="21" t="s">
         <v>160</v>
       </c>
@@ -10923,14 +10926,14 @@
       <c r="Q30" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="R30" s="167" t="s">
+      <c r="R30" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="S30" s="145"/>
-      <c r="T30" s="145"/>
-      <c r="U30" s="145"/>
-      <c r="V30" s="145"/>
-      <c r="W30" s="145"/>
+      <c r="S30" s="147"/>
+      <c r="T30" s="147"/>
+      <c r="U30" s="147"/>
+      <c r="V30" s="147"/>
+      <c r="W30" s="147"/>
       <c r="X30" s="21" t="s">
         <v>160</v>
       </c>
@@ -10961,14 +10964,14 @@
       <c r="AG30" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AH30" s="167" t="s">
+      <c r="AH30" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="AI30" s="145"/>
-      <c r="AJ30" s="145"/>
-      <c r="AK30" s="145"/>
-      <c r="AL30" s="145"/>
-      <c r="AM30" s="145"/>
+      <c r="AI30" s="147"/>
+      <c r="AJ30" s="147"/>
+      <c r="AK30" s="147"/>
+      <c r="AL30" s="147"/>
+      <c r="AM30" s="147"/>
       <c r="AN30" s="21" t="s">
         <v>160</v>
       </c>
@@ -11001,15 +11004,15 @@
       <c r="A31" s="22">
         <v>1</v>
       </c>
-      <c r="B31" s="163" t="str">
+      <c r="B31" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$39:$B$42,MATCH(1,Calc!$J$39:$J$42,0)),"?")</f>
         <v>Argentina</v>
       </c>
-      <c r="C31" s="145"/>
-      <c r="D31" s="145"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="145"/>
-      <c r="G31" s="145"/>
+      <c r="C31" s="147"/>
+      <c r="D31" s="147"/>
+      <c r="E31" s="147"/>
+      <c r="F31" s="147"/>
+      <c r="G31" s="147"/>
       <c r="H31" s="23">
         <f>IFERROR(INDEX(Calc!$H$39:$H$42,MATCH(1,Calc!$J$39:$J$42,0)),0)</f>
         <v>9</v>
@@ -11049,15 +11052,15 @@
       <c r="Q31" s="22">
         <v>1</v>
       </c>
-      <c r="R31" s="163" t="str">
+      <c r="R31" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$43:$B$46,MATCH(1,Calc!$J$43:$J$46,0)),"?")</f>
         <v>Portugal</v>
       </c>
-      <c r="S31" s="145"/>
-      <c r="T31" s="145"/>
-      <c r="U31" s="145"/>
-      <c r="V31" s="145"/>
-      <c r="W31" s="145"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="147"/>
+      <c r="U31" s="147"/>
+      <c r="V31" s="147"/>
+      <c r="W31" s="147"/>
       <c r="X31" s="23">
         <f>IFERROR(INDEX(Calc!$H$43:$H$46,MATCH(1,Calc!$J$43:$J$46,0)),0)</f>
         <v>5</v>
@@ -11097,15 +11100,15 @@
       <c r="AG31" s="22">
         <v>1</v>
       </c>
-      <c r="AH31" s="163" t="str">
+      <c r="AH31" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$47:$B$50,MATCH(1,Calc!$J$47:$J$50,0)),"?")</f>
         <v>Croacia</v>
       </c>
-      <c r="AI31" s="145"/>
-      <c r="AJ31" s="145"/>
-      <c r="AK31" s="145"/>
-      <c r="AL31" s="145"/>
-      <c r="AM31" s="145"/>
+      <c r="AI31" s="147"/>
+      <c r="AJ31" s="147"/>
+      <c r="AK31" s="147"/>
+      <c r="AL31" s="147"/>
+      <c r="AM31" s="147"/>
       <c r="AN31" s="23">
         <f>IFERROR(INDEX(Calc!$H$47:$H$50,MATCH(1,Calc!$J$47:$J$50,0)),0)</f>
         <v>9</v>
@@ -11147,15 +11150,15 @@
       <c r="A32" s="24">
         <v>2</v>
       </c>
-      <c r="B32" s="152" t="str">
+      <c r="B32" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$39:$B$42,MATCH(2,Calc!$J$39:$J$42,0)),"?")</f>
         <v>Austria</v>
       </c>
-      <c r="C32" s="145"/>
-      <c r="D32" s="145"/>
-      <c r="E32" s="145"/>
-      <c r="F32" s="145"/>
-      <c r="G32" s="145"/>
+      <c r="C32" s="147"/>
+      <c r="D32" s="147"/>
+      <c r="E32" s="147"/>
+      <c r="F32" s="147"/>
+      <c r="G32" s="147"/>
       <c r="H32" s="25">
         <f>IFERROR(INDEX(Calc!$H$39:$H$42,MATCH(2,Calc!$J$39:$J$42,0)),0)</f>
         <v>2</v>
@@ -11195,15 +11198,15 @@
       <c r="Q32" s="24">
         <v>2</v>
       </c>
-      <c r="R32" s="152" t="str">
+      <c r="R32" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$43:$B$46,MATCH(2,Calc!$J$43:$J$46,0)),"?")</f>
         <v>Colombia</v>
       </c>
-      <c r="S32" s="145"/>
-      <c r="T32" s="145"/>
-      <c r="U32" s="145"/>
-      <c r="V32" s="145"/>
-      <c r="W32" s="145"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="147"/>
+      <c r="U32" s="147"/>
+      <c r="V32" s="147"/>
+      <c r="W32" s="147"/>
       <c r="X32" s="25">
         <f>IFERROR(INDEX(Calc!$H$43:$H$46,MATCH(2,Calc!$J$43:$J$46,0)),0)</f>
         <v>5</v>
@@ -11243,15 +11246,15 @@
       <c r="AG32" s="24">
         <v>2</v>
       </c>
-      <c r="AH32" s="152" t="str">
+      <c r="AH32" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$47:$B$50,MATCH(2,Calc!$J$47:$J$50,0)),"?")</f>
         <v>Inglaterra</v>
       </c>
-      <c r="AI32" s="145"/>
-      <c r="AJ32" s="145"/>
-      <c r="AK32" s="145"/>
-      <c r="AL32" s="145"/>
-      <c r="AM32" s="145"/>
+      <c r="AI32" s="147"/>
+      <c r="AJ32" s="147"/>
+      <c r="AK32" s="147"/>
+      <c r="AL32" s="147"/>
+      <c r="AM32" s="147"/>
       <c r="AN32" s="25">
         <f>IFERROR(INDEX(Calc!$H$47:$H$50,MATCH(2,Calc!$J$47:$J$50,0)),0)</f>
         <v>6</v>
@@ -11293,15 +11296,15 @@
       <c r="A33" s="26">
         <v>3</v>
       </c>
-      <c r="B33" s="165" t="str">
+      <c r="B33" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$39:$B$42,MATCH(3,Calc!$J$39:$J$42,0)),"?")</f>
         <v>Jordania</v>
       </c>
-      <c r="C33" s="145"/>
-      <c r="D33" s="145"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="145"/>
+      <c r="C33" s="147"/>
+      <c r="D33" s="147"/>
+      <c r="E33" s="147"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="147"/>
       <c r="H33" s="27">
         <f>IFERROR(INDEX(Calc!$H$39:$H$42,MATCH(3,Calc!$J$39:$J$42,0)),0)</f>
         <v>2</v>
@@ -11341,15 +11344,15 @@
       <c r="Q33" s="26">
         <v>3</v>
       </c>
-      <c r="R33" s="165" t="str">
+      <c r="R33" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$43:$B$46,MATCH(3,Calc!$J$43:$J$46,0)),"?")</f>
         <v>Uzbequistao</v>
       </c>
-      <c r="S33" s="145"/>
-      <c r="T33" s="145"/>
-      <c r="U33" s="145"/>
-      <c r="V33" s="145"/>
-      <c r="W33" s="145"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="147"/>
+      <c r="U33" s="147"/>
+      <c r="V33" s="147"/>
+      <c r="W33" s="147"/>
       <c r="X33" s="27">
         <f>IFERROR(INDEX(Calc!$H$43:$H$46,MATCH(3,Calc!$J$43:$J$46,0)),0)</f>
         <v>3</v>
@@ -11389,15 +11392,15 @@
       <c r="AG33" s="26">
         <v>3</v>
       </c>
-      <c r="AH33" s="165" t="str">
+      <c r="AH33" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$47:$B$50,MATCH(3,Calc!$J$47:$J$50,0)),"?")</f>
         <v>Gana</v>
       </c>
-      <c r="AI33" s="145"/>
-      <c r="AJ33" s="145"/>
-      <c r="AK33" s="145"/>
-      <c r="AL33" s="145"/>
-      <c r="AM33" s="145"/>
+      <c r="AI33" s="147"/>
+      <c r="AJ33" s="147"/>
+      <c r="AK33" s="147"/>
+      <c r="AL33" s="147"/>
+      <c r="AM33" s="147"/>
       <c r="AN33" s="27">
         <f>IFERROR(INDEX(Calc!$H$47:$H$50,MATCH(3,Calc!$J$47:$J$50,0)),0)</f>
         <v>1</v>
@@ -11439,15 +11442,15 @@
       <c r="A34" s="28">
         <v>4</v>
       </c>
-      <c r="B34" s="164" t="str">
+      <c r="B34" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$39:$B$42,MATCH(4,Calc!$J$39:$J$42,0)),"?")</f>
         <v>Argelia</v>
       </c>
-      <c r="C34" s="145"/>
-      <c r="D34" s="145"/>
-      <c r="E34" s="145"/>
-      <c r="F34" s="145"/>
-      <c r="G34" s="145"/>
+      <c r="C34" s="147"/>
+      <c r="D34" s="147"/>
+      <c r="E34" s="147"/>
+      <c r="F34" s="147"/>
+      <c r="G34" s="147"/>
       <c r="H34" s="29">
         <f>IFERROR(INDEX(Calc!$H$39:$H$42,MATCH(4,Calc!$J$39:$J$42,0)),0)</f>
         <v>2</v>
@@ -11487,15 +11490,15 @@
       <c r="Q34" s="28">
         <v>4</v>
       </c>
-      <c r="R34" s="164" t="str">
+      <c r="R34" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$43:$B$46,MATCH(4,Calc!$J$43:$J$46,0)),"?")</f>
         <v>RD Congo</v>
       </c>
-      <c r="S34" s="145"/>
-      <c r="T34" s="145"/>
-      <c r="U34" s="145"/>
-      <c r="V34" s="145"/>
-      <c r="W34" s="145"/>
+      <c r="S34" s="147"/>
+      <c r="T34" s="147"/>
+      <c r="U34" s="147"/>
+      <c r="V34" s="147"/>
+      <c r="W34" s="147"/>
       <c r="X34" s="29">
         <f>IFERROR(INDEX(Calc!$H$43:$H$46,MATCH(4,Calc!$J$43:$J$46,0)),0)</f>
         <v>1</v>
@@ -11535,15 +11538,15 @@
       <c r="AG34" s="28">
         <v>4</v>
       </c>
-      <c r="AH34" s="164" t="str">
+      <c r="AH34" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$47:$B$50,MATCH(4,Calc!$J$47:$J$50,0)),"?")</f>
         <v>Panama</v>
       </c>
-      <c r="AI34" s="145"/>
-      <c r="AJ34" s="145"/>
-      <c r="AK34" s="145"/>
-      <c r="AL34" s="145"/>
-      <c r="AM34" s="145"/>
+      <c r="AI34" s="147"/>
+      <c r="AJ34" s="147"/>
+      <c r="AK34" s="147"/>
+      <c r="AL34" s="147"/>
+      <c r="AM34" s="147"/>
       <c r="AN34" s="29">
         <f>IFERROR(INDEX(Calc!$H$47:$H$50,MATCH(4,Calc!$J$47:$J$50,0)),0)</f>
         <v>1</v>
@@ -11583,6 +11586,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="R18:W18"/>
+    <mergeCell ref="BT3:BU3"/>
+    <mergeCell ref="CF3:CG3"/>
+    <mergeCell ref="AG15:AU15"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="EJ3:EK3"/>
+    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="AG8:AU8"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="CB3:CC3"/>
+    <mergeCell ref="DJ3:DK3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="R13:W13"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AH20:AM20"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="R12:W12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="AG29:AU29"/>
+    <mergeCell ref="AH23:AM23"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="AH9:AM9"/>
+    <mergeCell ref="AG22:AU22"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="R26:W26"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A2:EO2"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="R10:W10"/>
+    <mergeCell ref="AH24:AM24"/>
+    <mergeCell ref="DL3:DM3"/>
+    <mergeCell ref="R19:W19"/>
+    <mergeCell ref="AH18:AM18"/>
+    <mergeCell ref="BV3:BW3"/>
+    <mergeCell ref="DN3:DO3"/>
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="AH17:AM17"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="AH11:AM11"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="R23:W23"/>
+    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="R34:W34"/>
+    <mergeCell ref="R16:W16"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="R27:W27"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="R24:W24"/>
+    <mergeCell ref="R33:W33"/>
+    <mergeCell ref="AH33:AM33"/>
+    <mergeCell ref="R30:W30"/>
+    <mergeCell ref="R25:W25"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="AH19:AM19"/>
+    <mergeCell ref="AH26:AM26"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="AH34:AM34"/>
+    <mergeCell ref="AH27:AM27"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="R31:W31"/>
+    <mergeCell ref="R32:W32"/>
+    <mergeCell ref="AH30:AM30"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AH32:AM32"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="AH31:AM31"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="AH16:AM16"/>
+    <mergeCell ref="AH25:AM25"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="EL3:EM3"/>
     <mergeCell ref="CV3:CW3"/>
     <mergeCell ref="EN3:EO3"/>
@@ -11607,129 +11733,6 @@
     <mergeCell ref="R11:W11"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="AH34:AM34"/>
-    <mergeCell ref="AH27:AM27"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="R31:W31"/>
-    <mergeCell ref="R32:W32"/>
-    <mergeCell ref="AH30:AM30"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AH32:AM32"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="AH31:AM31"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="AH25:AM25"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="R34:W34"/>
-    <mergeCell ref="R16:W16"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="CJ3:CK3"/>
-    <mergeCell ref="CL3:CM3"/>
-    <mergeCell ref="R27:W27"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="R24:W24"/>
-    <mergeCell ref="R33:W33"/>
-    <mergeCell ref="AH33:AM33"/>
-    <mergeCell ref="R30:W30"/>
-    <mergeCell ref="R25:W25"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="AH19:AM19"/>
-    <mergeCell ref="AH26:AM26"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="A2:EO2"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="R10:W10"/>
-    <mergeCell ref="AH24:AM24"/>
-    <mergeCell ref="DL3:DM3"/>
-    <mergeCell ref="R19:W19"/>
-    <mergeCell ref="AH18:AM18"/>
-    <mergeCell ref="BV3:BW3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="AH17:AM17"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="AH11:AM11"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="R23:W23"/>
-    <mergeCell ref="AH13:AM13"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="R13:W13"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AH20:AM20"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="R12:W12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="AG29:AU29"/>
-    <mergeCell ref="AH23:AM23"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="AH9:AM9"/>
-    <mergeCell ref="AG22:AU22"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="R26:W26"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="EJ3:EK3"/>
-    <mergeCell ref="CT3:CU3"/>
-    <mergeCell ref="AG8:AU8"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="CB3:CC3"/>
-    <mergeCell ref="DJ3:DK3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="R18:W18"/>
-    <mergeCell ref="BT3:BU3"/>
-    <mergeCell ref="CF3:CG3"/>
-    <mergeCell ref="AG15:AU15"/>
-    <mergeCell ref="A15:O15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11737,12 +11740,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF50B69-7C30-4E8D-8A33-5820F111502A}">
-  <dimension ref="A1:D817"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D818"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -15497,7 +15500,7 @@
         <v>116</v>
       </c>
       <c r="B451" s="128" t="s">
-        <v>1212</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -15505,7 +15508,7 @@
         <v>116</v>
       </c>
       <c r="B452" s="128" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -15513,7 +15516,7 @@
         <v>116</v>
       </c>
       <c r="B453" s="128" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -15521,7 +15524,7 @@
         <v>116</v>
       </c>
       <c r="B454" s="128" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -15529,7 +15532,7 @@
         <v>116</v>
       </c>
       <c r="B455" s="128" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -15537,7 +15540,7 @@
         <v>116</v>
       </c>
       <c r="B456" s="128" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -15545,7 +15548,7 @@
         <v>116</v>
       </c>
       <c r="B457" s="128" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -15553,7 +15556,7 @@
         <v>116</v>
       </c>
       <c r="B458" s="128" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -15561,7 +15564,7 @@
         <v>116</v>
       </c>
       <c r="B459" s="128" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -15569,7 +15572,7 @@
         <v>116</v>
       </c>
       <c r="B460" s="128" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -15577,7 +15580,7 @@
         <v>116</v>
       </c>
       <c r="B461" s="128" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -15585,15 +15588,15 @@
         <v>116</v>
       </c>
       <c r="B462" s="128" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" s="128" t="s">
-        <v>1224</v>
+        <v>116</v>
       </c>
       <c r="B463" s="128" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -15601,7 +15604,7 @@
         <v>1224</v>
       </c>
       <c r="B464" s="128" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -15609,7 +15612,7 @@
         <v>1224</v>
       </c>
       <c r="B465" s="128" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -15617,7 +15620,7 @@
         <v>1224</v>
       </c>
       <c r="B466" s="128" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -15625,7 +15628,7 @@
         <v>1224</v>
       </c>
       <c r="B467" s="128" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -15633,7 +15636,7 @@
         <v>1224</v>
       </c>
       <c r="B468" s="128" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -15641,7 +15644,7 @@
         <v>1224</v>
       </c>
       <c r="B469" s="128" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -15649,7 +15652,7 @@
         <v>1224</v>
       </c>
       <c r="B470" s="128" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -15657,7 +15660,7 @@
         <v>1224</v>
       </c>
       <c r="B471" s="128" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -15665,7 +15668,7 @@
         <v>1224</v>
       </c>
       <c r="B472" s="128" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -15673,7 +15676,7 @@
         <v>1224</v>
       </c>
       <c r="B473" s="128" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -15681,7 +15684,7 @@
         <v>1224</v>
       </c>
       <c r="B474" s="128" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -15689,7 +15692,7 @@
         <v>1224</v>
       </c>
       <c r="B475" s="128" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -15697,7 +15700,7 @@
         <v>1224</v>
       </c>
       <c r="B476" s="128" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -15705,7 +15708,7 @@
         <v>1224</v>
       </c>
       <c r="B477" s="128" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -15713,7 +15716,7 @@
         <v>1224</v>
       </c>
       <c r="B478" s="128" t="s">
-        <v>1590</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -15721,7 +15724,7 @@
         <v>1224</v>
       </c>
       <c r="B479" s="128" t="s">
-        <v>1240</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -15729,15 +15732,15 @@
         <v>1224</v>
       </c>
       <c r="B480" s="128" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" s="128" t="s">
-        <v>127</v>
+        <v>1224</v>
       </c>
       <c r="B481" s="128" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -15745,7 +15748,7 @@
         <v>127</v>
       </c>
       <c r="B482" s="128" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -15753,7 +15756,7 @@
         <v>127</v>
       </c>
       <c r="B483" s="128" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -15761,7 +15764,7 @@
         <v>127</v>
       </c>
       <c r="B484" s="128" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -15769,7 +15772,7 @@
         <v>127</v>
       </c>
       <c r="B485" s="128" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -15777,7 +15780,7 @@
         <v>127</v>
       </c>
       <c r="B486" s="128" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -15785,7 +15788,7 @@
         <v>127</v>
       </c>
       <c r="B487" s="128" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -15793,7 +15796,7 @@
         <v>127</v>
       </c>
       <c r="B488" s="128" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -15801,7 +15804,7 @@
         <v>127</v>
       </c>
       <c r="B489" s="128" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -15809,7 +15812,7 @@
         <v>127</v>
       </c>
       <c r="B490" s="128" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -15817,7 +15820,7 @@
         <v>127</v>
       </c>
       <c r="B491" s="128" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -15825,7 +15828,7 @@
         <v>127</v>
       </c>
       <c r="B492" s="128" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -15833,7 +15836,7 @@
         <v>127</v>
       </c>
       <c r="B493" s="128" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -15841,7 +15844,7 @@
         <v>127</v>
       </c>
       <c r="B494" s="128" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -15849,7 +15852,7 @@
         <v>127</v>
       </c>
       <c r="B495" s="128" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -15857,15 +15860,15 @@
         <v>127</v>
       </c>
       <c r="B496" s="128" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" s="128" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B497" s="128" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -15873,7 +15876,7 @@
         <v>121</v>
       </c>
       <c r="B498" s="128" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -15881,7 +15884,7 @@
         <v>121</v>
       </c>
       <c r="B499" s="128" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -15889,7 +15892,7 @@
         <v>121</v>
       </c>
       <c r="B500" s="128" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -15897,7 +15900,7 @@
         <v>121</v>
       </c>
       <c r="B501" s="128" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -15905,7 +15908,7 @@
         <v>121</v>
       </c>
       <c r="B502" s="128" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -15913,7 +15916,7 @@
         <v>121</v>
       </c>
       <c r="B503" s="128" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -15921,7 +15924,7 @@
         <v>121</v>
       </c>
       <c r="B504" s="128" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -15929,7 +15932,7 @@
         <v>121</v>
       </c>
       <c r="B505" s="128" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -15937,7 +15940,7 @@
         <v>121</v>
       </c>
       <c r="B506" s="128" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -15945,7 +15948,7 @@
         <v>121</v>
       </c>
       <c r="B507" s="128" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -15953,7 +15956,7 @@
         <v>121</v>
       </c>
       <c r="B508" s="128" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -15961,7 +15964,7 @@
         <v>121</v>
       </c>
       <c r="B509" s="128" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -15969,7 +15972,7 @@
         <v>121</v>
       </c>
       <c r="B510" s="128" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -15977,15 +15980,15 @@
         <v>121</v>
       </c>
       <c r="B511" s="128" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" s="128" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="B512" s="128" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -15993,7 +15996,7 @@
         <v>139</v>
       </c>
       <c r="B513" s="128" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -16001,7 +16004,7 @@
         <v>139</v>
       </c>
       <c r="B514" s="128" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -16009,7 +16012,7 @@
         <v>139</v>
       </c>
       <c r="B515" s="128" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -16017,7 +16020,7 @@
         <v>139</v>
       </c>
       <c r="B516" s="128" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -16025,7 +16028,7 @@
         <v>139</v>
       </c>
       <c r="B517" s="128" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -16033,7 +16036,7 @@
         <v>139</v>
       </c>
       <c r="B518" s="128" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -16041,7 +16044,7 @@
         <v>139</v>
       </c>
       <c r="B519" s="128" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -16049,7 +16052,7 @@
         <v>139</v>
       </c>
       <c r="B520" s="128" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -16057,7 +16060,7 @@
         <v>139</v>
       </c>
       <c r="B521" s="128" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -16065,7 +16068,7 @@
         <v>139</v>
       </c>
       <c r="B522" s="128" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -16073,7 +16076,7 @@
         <v>139</v>
       </c>
       <c r="B523" s="128" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -16081,7 +16084,7 @@
         <v>139</v>
       </c>
       <c r="B524" s="128" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -16089,7 +16092,7 @@
         <v>139</v>
       </c>
       <c r="B525" s="128" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -16097,7 +16100,7 @@
         <v>139</v>
       </c>
       <c r="B526" s="128" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -16105,7 +16108,7 @@
         <v>139</v>
       </c>
       <c r="B527" s="128" t="s">
-        <v>1589</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -16113,7 +16116,7 @@
         <v>139</v>
       </c>
       <c r="B528" s="128" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -16121,7 +16124,7 @@
         <v>139</v>
       </c>
       <c r="B529" s="128" t="s">
-        <v>1288</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -16129,15 +16132,15 @@
         <v>139</v>
       </c>
       <c r="B530" s="128" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" s="128" t="s">
-        <v>1290</v>
+        <v>139</v>
       </c>
       <c r="B531" s="128" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -16145,7 +16148,7 @@
         <v>1290</v>
       </c>
       <c r="B532" s="128" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -16153,7 +16156,7 @@
         <v>1290</v>
       </c>
       <c r="B533" s="128" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -16161,7 +16164,7 @@
         <v>1290</v>
       </c>
       <c r="B534" s="128" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -16169,7 +16172,7 @@
         <v>1290</v>
       </c>
       <c r="B535" s="128" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -16177,7 +16180,7 @@
         <v>1290</v>
       </c>
       <c r="B536" s="128" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -16185,7 +16188,7 @@
         <v>1290</v>
       </c>
       <c r="B537" s="128" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -16193,7 +16196,7 @@
         <v>1290</v>
       </c>
       <c r="B538" s="128" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -16201,7 +16204,7 @@
         <v>1290</v>
       </c>
       <c r="B539" s="128" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -16209,7 +16212,7 @@
         <v>1290</v>
       </c>
       <c r="B540" s="128" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -16217,7 +16220,7 @@
         <v>1290</v>
       </c>
       <c r="B541" s="128" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -16225,7 +16228,7 @@
         <v>1290</v>
       </c>
       <c r="B542" s="128" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -16233,7 +16236,7 @@
         <v>1290</v>
       </c>
       <c r="B543" s="128" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -16241,15 +16244,15 @@
         <v>1290</v>
       </c>
       <c r="B544" s="128" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" s="128" t="s">
-        <v>1305</v>
+        <v>1290</v>
       </c>
       <c r="B545" s="128" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -16257,7 +16260,7 @@
         <v>1305</v>
       </c>
       <c r="B546" s="128" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -16265,7 +16268,7 @@
         <v>1305</v>
       </c>
       <c r="B547" s="128" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -16273,7 +16276,7 @@
         <v>1305</v>
       </c>
       <c r="B548" s="128" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -16281,7 +16284,7 @@
         <v>1305</v>
       </c>
       <c r="B549" s="128" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -16289,7 +16292,7 @@
         <v>1305</v>
       </c>
       <c r="B550" s="128" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -16297,7 +16300,7 @@
         <v>1305</v>
       </c>
       <c r="B551" s="128" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -16305,7 +16308,7 @@
         <v>1305</v>
       </c>
       <c r="B552" s="128" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -16313,7 +16316,7 @@
         <v>1305</v>
       </c>
       <c r="B553" s="128" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -16321,7 +16324,7 @@
         <v>1305</v>
       </c>
       <c r="B554" s="128" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -16329,7 +16332,7 @@
         <v>1305</v>
       </c>
       <c r="B555" s="128" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -16337,7 +16340,7 @@
         <v>1305</v>
       </c>
       <c r="B556" s="128" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -16345,7 +16348,7 @@
         <v>1305</v>
       </c>
       <c r="B557" s="128" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -16353,7 +16356,7 @@
         <v>1305</v>
       </c>
       <c r="B558" s="128" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -16361,7 +16364,7 @@
         <v>1305</v>
       </c>
       <c r="B559" s="128" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -16369,15 +16372,15 @@
         <v>1305</v>
       </c>
       <c r="B560" s="128" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" s="128" t="s">
-        <v>1322</v>
+        <v>1305</v>
       </c>
       <c r="B561" s="128" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -16385,7 +16388,7 @@
         <v>1322</v>
       </c>
       <c r="B562" s="128" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -16393,7 +16396,7 @@
         <v>1322</v>
       </c>
       <c r="B563" s="128" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -16401,7 +16404,7 @@
         <v>1322</v>
       </c>
       <c r="B564" s="128" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -16409,7 +16412,7 @@
         <v>1322</v>
       </c>
       <c r="B565" s="128" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -16417,7 +16420,7 @@
         <v>1322</v>
       </c>
       <c r="B566" s="128" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -16425,7 +16428,7 @@
         <v>1322</v>
       </c>
       <c r="B567" s="128" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -16433,7 +16436,7 @@
         <v>1322</v>
       </c>
       <c r="B568" s="128" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -16441,7 +16444,7 @@
         <v>1322</v>
       </c>
       <c r="B569" s="128" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -16449,7 +16452,7 @@
         <v>1322</v>
       </c>
       <c r="B570" s="128" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -16457,7 +16460,7 @@
         <v>1322</v>
       </c>
       <c r="B571" s="128" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -16465,7 +16468,7 @@
         <v>1322</v>
       </c>
       <c r="B572" s="128" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -16473,7 +16476,7 @@
         <v>1322</v>
       </c>
       <c r="B573" s="128" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -16481,7 +16484,7 @@
         <v>1322</v>
       </c>
       <c r="B574" s="128" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -16489,7 +16492,7 @@
         <v>1322</v>
       </c>
       <c r="B575" s="128" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -16497,7 +16500,7 @@
         <v>1322</v>
       </c>
       <c r="B576" s="128" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -16505,7 +16508,7 @@
         <v>1322</v>
       </c>
       <c r="B577" s="128" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -16513,15 +16516,15 @@
         <v>1322</v>
       </c>
       <c r="B578" s="128" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" s="128" t="s">
-        <v>1341</v>
+        <v>1322</v>
       </c>
       <c r="B579" s="128" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -16529,7 +16532,7 @@
         <v>1341</v>
       </c>
       <c r="B580" s="128" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -16537,7 +16540,7 @@
         <v>1341</v>
       </c>
       <c r="B581" s="128" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -16545,7 +16548,7 @@
         <v>1341</v>
       </c>
       <c r="B582" s="128" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -16553,7 +16556,7 @@
         <v>1341</v>
       </c>
       <c r="B583" s="128" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -16561,7 +16564,7 @@
         <v>1341</v>
       </c>
       <c r="B584" s="128" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -16569,7 +16572,7 @@
         <v>1341</v>
       </c>
       <c r="B585" s="128" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -16577,7 +16580,7 @@
         <v>1341</v>
       </c>
       <c r="B586" s="128" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -16585,7 +16588,7 @@
         <v>1341</v>
       </c>
       <c r="B587" s="128" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -16593,7 +16596,7 @@
         <v>1341</v>
       </c>
       <c r="B588" s="128" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -16601,7 +16604,7 @@
         <v>1341</v>
       </c>
       <c r="B589" s="128" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -16609,7 +16612,7 @@
         <v>1341</v>
       </c>
       <c r="B590" s="128" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -16617,7 +16620,7 @@
         <v>1341</v>
       </c>
       <c r="B591" s="128" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -16625,15 +16628,15 @@
         <v>1341</v>
       </c>
       <c r="B592" s="128" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" s="128" t="s">
-        <v>1356</v>
+        <v>1341</v>
       </c>
       <c r="B593" s="128" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -16641,7 +16644,7 @@
         <v>1356</v>
       </c>
       <c r="B594" s="128" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -16649,7 +16652,7 @@
         <v>1356</v>
       </c>
       <c r="B595" s="128" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -16657,7 +16660,7 @@
         <v>1356</v>
       </c>
       <c r="B596" s="128" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -16665,7 +16668,7 @@
         <v>1356</v>
       </c>
       <c r="B597" s="128" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -16673,7 +16676,7 @@
         <v>1356</v>
       </c>
       <c r="B598" s="128" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -16681,7 +16684,7 @@
         <v>1356</v>
       </c>
       <c r="B599" s="128" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -16689,7 +16692,7 @@
         <v>1356</v>
       </c>
       <c r="B600" s="128" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -16697,7 +16700,7 @@
         <v>1356</v>
       </c>
       <c r="B601" s="128" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -16705,7 +16708,7 @@
         <v>1356</v>
       </c>
       <c r="B602" s="128" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -16713,7 +16716,7 @@
         <v>1356</v>
       </c>
       <c r="B603" s="128" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -16721,7 +16724,7 @@
         <v>1356</v>
       </c>
       <c r="B604" s="128" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -16729,7 +16732,7 @@
         <v>1356</v>
       </c>
       <c r="B605" s="128" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -16737,7 +16740,7 @@
         <v>1356</v>
       </c>
       <c r="B606" s="128" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -16745,7 +16748,7 @@
         <v>1356</v>
       </c>
       <c r="B607" s="128" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -16753,7 +16756,7 @@
         <v>1356</v>
       </c>
       <c r="B608" s="128" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -16761,15 +16764,15 @@
         <v>1356</v>
       </c>
       <c r="B609" s="128" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" s="128" t="s">
-        <v>1374</v>
+        <v>1356</v>
       </c>
       <c r="B610" s="128" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -16777,7 +16780,7 @@
         <v>1374</v>
       </c>
       <c r="B611" s="128" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -16785,7 +16788,7 @@
         <v>1374</v>
       </c>
       <c r="B612" s="128" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -16793,7 +16796,7 @@
         <v>1374</v>
       </c>
       <c r="B613" s="128" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -16801,7 +16804,7 @@
         <v>1374</v>
       </c>
       <c r="B614" s="128" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -16809,7 +16812,7 @@
         <v>1374</v>
       </c>
       <c r="B615" s="128" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -16817,7 +16820,7 @@
         <v>1374</v>
       </c>
       <c r="B616" s="128" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -16825,7 +16828,7 @@
         <v>1374</v>
       </c>
       <c r="B617" s="128" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -16833,7 +16836,7 @@
         <v>1374</v>
       </c>
       <c r="B618" s="128" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -16841,7 +16844,7 @@
         <v>1374</v>
       </c>
       <c r="B619" s="128" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -16849,7 +16852,7 @@
         <v>1374</v>
       </c>
       <c r="B620" s="128" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -16857,7 +16860,7 @@
         <v>1374</v>
       </c>
       <c r="B621" s="128" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -16865,7 +16868,7 @@
         <v>1374</v>
       </c>
       <c r="B622" s="128" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -16873,7 +16876,7 @@
         <v>1374</v>
       </c>
       <c r="B623" s="128" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -16881,15 +16884,15 @@
         <v>1374</v>
       </c>
       <c r="B624" s="128" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" s="128" t="s">
-        <v>152</v>
+        <v>1374</v>
       </c>
       <c r="B625" s="128" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -16897,7 +16900,7 @@
         <v>152</v>
       </c>
       <c r="B626" s="128" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -16905,7 +16908,7 @@
         <v>152</v>
       </c>
       <c r="B627" s="128" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -16913,7 +16916,7 @@
         <v>152</v>
       </c>
       <c r="B628" s="128" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -16921,7 +16924,7 @@
         <v>152</v>
       </c>
       <c r="B629" s="128" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -16929,7 +16932,7 @@
         <v>152</v>
       </c>
       <c r="B630" s="128" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -16937,7 +16940,7 @@
         <v>152</v>
       </c>
       <c r="B631" s="128" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -16945,7 +16948,7 @@
         <v>152</v>
       </c>
       <c r="B632" s="128" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -16953,7 +16956,7 @@
         <v>152</v>
       </c>
       <c r="B633" s="128" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -16961,7 +16964,7 @@
         <v>152</v>
       </c>
       <c r="B634" s="128" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -16969,7 +16972,7 @@
         <v>152</v>
       </c>
       <c r="B635" s="128" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -16977,7 +16980,7 @@
         <v>152</v>
       </c>
       <c r="B636" s="128" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -16985,7 +16988,7 @@
         <v>152</v>
       </c>
       <c r="B637" s="128" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -16993,7 +16996,7 @@
         <v>152</v>
       </c>
       <c r="B638" s="128" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -17001,7 +17004,7 @@
         <v>152</v>
       </c>
       <c r="B639" s="128" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -17009,7 +17012,7 @@
         <v>152</v>
       </c>
       <c r="B640" s="128" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -17017,7 +17020,7 @@
         <v>152</v>
       </c>
       <c r="B641" s="128" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -17025,7 +17028,7 @@
         <v>152</v>
       </c>
       <c r="B642" s="128" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -17033,7 +17036,7 @@
         <v>152</v>
       </c>
       <c r="B643" s="128" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -17041,15 +17044,15 @@
         <v>152</v>
       </c>
       <c r="B644" s="128" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" s="128" t="s">
-        <v>1410</v>
+        <v>152</v>
       </c>
       <c r="B645" s="128" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -17057,7 +17060,7 @@
         <v>1410</v>
       </c>
       <c r="B646" s="128" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -17065,7 +17068,7 @@
         <v>1410</v>
       </c>
       <c r="B647" s="128" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -17073,7 +17076,7 @@
         <v>1410</v>
       </c>
       <c r="B648" s="128" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -17081,7 +17084,7 @@
         <v>1410</v>
       </c>
       <c r="B649" s="128" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -17089,7 +17092,7 @@
         <v>1410</v>
       </c>
       <c r="B650" s="128" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -17097,7 +17100,7 @@
         <v>1410</v>
       </c>
       <c r="B651" s="128" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -17105,7 +17108,7 @@
         <v>1410</v>
       </c>
       <c r="B652" s="128" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -17113,7 +17116,7 @@
         <v>1410</v>
       </c>
       <c r="B653" s="128" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -17121,7 +17124,7 @@
         <v>1410</v>
       </c>
       <c r="B654" s="128" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -17129,7 +17132,7 @@
         <v>1410</v>
       </c>
       <c r="B655" s="128" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -17137,7 +17140,7 @@
         <v>1410</v>
       </c>
       <c r="B656" s="128" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -17145,7 +17148,7 @@
         <v>1410</v>
       </c>
       <c r="B657" s="128" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -17153,7 +17156,7 @@
         <v>1410</v>
       </c>
       <c r="B658" s="128" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -17161,7 +17164,7 @@
         <v>1410</v>
       </c>
       <c r="B659" s="128" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -17169,7 +17172,7 @@
         <v>1410</v>
       </c>
       <c r="B660" s="128" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -17177,7 +17180,7 @@
         <v>1410</v>
       </c>
       <c r="B661" s="128" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -17185,7 +17188,7 @@
         <v>1410</v>
       </c>
       <c r="B662" s="128" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -17193,15 +17196,15 @@
         <v>1410</v>
       </c>
       <c r="B663" s="128" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" s="128" t="s">
-        <v>124</v>
+        <v>1410</v>
       </c>
       <c r="B664" s="128" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -17209,7 +17212,7 @@
         <v>124</v>
       </c>
       <c r="B665" s="128" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -17217,7 +17220,7 @@
         <v>124</v>
       </c>
       <c r="B666" s="128" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -17225,7 +17228,7 @@
         <v>124</v>
       </c>
       <c r="B667" s="128" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -17233,7 +17236,7 @@
         <v>124</v>
       </c>
       <c r="B668" s="128" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -17241,7 +17244,7 @@
         <v>124</v>
       </c>
       <c r="B669" s="128" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -17249,7 +17252,7 @@
         <v>124</v>
       </c>
       <c r="B670" s="128" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -17257,7 +17260,7 @@
         <v>124</v>
       </c>
       <c r="B671" s="128" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -17265,7 +17268,7 @@
         <v>124</v>
       </c>
       <c r="B672" s="128" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -17273,7 +17276,7 @@
         <v>124</v>
       </c>
       <c r="B673" s="128" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -17281,7 +17284,7 @@
         <v>124</v>
       </c>
       <c r="B674" s="128" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -17289,7 +17292,7 @@
         <v>124</v>
       </c>
       <c r="B675" s="128" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -17297,7 +17300,7 @@
         <v>124</v>
       </c>
       <c r="B676" s="128" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -17305,7 +17308,7 @@
         <v>124</v>
       </c>
       <c r="B677" s="128" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -17313,7 +17316,7 @@
         <v>124</v>
       </c>
       <c r="B678" s="128" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -17321,7 +17324,7 @@
         <v>124</v>
       </c>
       <c r="B679" s="128" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -17329,7 +17332,7 @@
         <v>124</v>
       </c>
       <c r="B680" s="128" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -17337,15 +17340,15 @@
         <v>124</v>
       </c>
       <c r="B681" s="128" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" s="128" t="s">
-        <v>1448</v>
+        <v>124</v>
       </c>
       <c r="B682" s="128" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -17353,7 +17356,7 @@
         <v>1448</v>
       </c>
       <c r="B683" s="128" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -17361,7 +17364,7 @@
         <v>1448</v>
       </c>
       <c r="B684" s="128" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -17369,7 +17372,7 @@
         <v>1448</v>
       </c>
       <c r="B685" s="128" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -17377,7 +17380,7 @@
         <v>1448</v>
       </c>
       <c r="B686" s="128" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -17385,7 +17388,7 @@
         <v>1448</v>
       </c>
       <c r="B687" s="128" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -17393,7 +17396,7 @@
         <v>1448</v>
       </c>
       <c r="B688" s="128" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -17401,7 +17404,7 @@
         <v>1448</v>
       </c>
       <c r="B689" s="128" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -17409,7 +17412,7 @@
         <v>1448</v>
       </c>
       <c r="B690" s="128" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -17417,7 +17420,7 @@
         <v>1448</v>
       </c>
       <c r="B691" s="128" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -17425,7 +17428,7 @@
         <v>1448</v>
       </c>
       <c r="B692" s="128" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -17433,7 +17436,7 @@
         <v>1448</v>
       </c>
       <c r="B693" s="128" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -17441,7 +17444,7 @@
         <v>1448</v>
       </c>
       <c r="B694" s="128" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -17449,7 +17452,7 @@
         <v>1448</v>
       </c>
       <c r="B695" s="128" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -17457,7 +17460,7 @@
         <v>1448</v>
       </c>
       <c r="B696" s="128" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -17465,7 +17468,7 @@
         <v>1448</v>
       </c>
       <c r="B697" s="128" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -17473,7 +17476,7 @@
         <v>1448</v>
       </c>
       <c r="B698" s="128" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -17481,15 +17484,15 @@
         <v>1448</v>
       </c>
       <c r="B699" s="128" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" s="128" t="s">
-        <v>143</v>
+        <v>1448</v>
       </c>
       <c r="B700" s="128" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -17497,7 +17500,7 @@
         <v>143</v>
       </c>
       <c r="B701" s="128" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -17505,7 +17508,7 @@
         <v>143</v>
       </c>
       <c r="B702" s="128" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -17513,7 +17516,7 @@
         <v>143</v>
       </c>
       <c r="B703" s="128" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -17521,7 +17524,7 @@
         <v>143</v>
       </c>
       <c r="B704" s="128" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -17529,7 +17532,7 @@
         <v>143</v>
       </c>
       <c r="B705" s="128" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -17537,7 +17540,7 @@
         <v>143</v>
       </c>
       <c r="B706" s="128" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -17545,7 +17548,7 @@
         <v>143</v>
       </c>
       <c r="B707" s="128" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -17553,7 +17556,7 @@
         <v>143</v>
       </c>
       <c r="B708" s="128" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -17561,7 +17564,7 @@
         <v>143</v>
       </c>
       <c r="B709" s="128" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -17569,7 +17572,7 @@
         <v>143</v>
       </c>
       <c r="B710" s="128" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -17577,7 +17580,7 @@
         <v>143</v>
       </c>
       <c r="B711" s="128" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -17585,7 +17588,7 @@
         <v>143</v>
       </c>
       <c r="B712" s="128" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -17593,7 +17596,7 @@
         <v>143</v>
       </c>
       <c r="B713" s="128" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -17601,15 +17604,15 @@
         <v>143</v>
       </c>
       <c r="B714" s="128" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" s="128" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B715" s="128" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -17617,7 +17620,7 @@
         <v>148</v>
       </c>
       <c r="B716" s="128" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -17625,7 +17628,7 @@
         <v>148</v>
       </c>
       <c r="B717" s="128" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -17633,7 +17636,7 @@
         <v>148</v>
       </c>
       <c r="B718" s="128" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -17641,7 +17644,7 @@
         <v>148</v>
       </c>
       <c r="B719" s="128" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -17649,7 +17652,7 @@
         <v>148</v>
       </c>
       <c r="B720" s="128" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -17657,7 +17660,7 @@
         <v>148</v>
       </c>
       <c r="B721" s="128" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -17665,7 +17668,7 @@
         <v>148</v>
       </c>
       <c r="B722" s="128" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -17673,7 +17676,7 @@
         <v>148</v>
       </c>
       <c r="B723" s="128" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -17681,7 +17684,7 @@
         <v>148</v>
       </c>
       <c r="B724" s="128" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -17689,7 +17692,7 @@
         <v>148</v>
       </c>
       <c r="B725" s="128" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -17697,7 +17700,7 @@
         <v>148</v>
       </c>
       <c r="B726" s="128" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -17705,7 +17708,7 @@
         <v>148</v>
       </c>
       <c r="B727" s="128" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -17713,7 +17716,7 @@
         <v>148</v>
       </c>
       <c r="B728" s="128" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -17721,7 +17724,7 @@
         <v>148</v>
       </c>
       <c r="B729" s="128" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -17729,7 +17732,7 @@
         <v>148</v>
       </c>
       <c r="B730" s="128" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -17737,7 +17740,7 @@
         <v>148</v>
       </c>
       <c r="B731" s="128" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -17745,7 +17748,7 @@
         <v>148</v>
       </c>
       <c r="B732" s="128" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -17753,15 +17756,15 @@
         <v>148</v>
       </c>
       <c r="B733" s="128" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" s="128" t="s">
-        <v>1501</v>
+        <v>148</v>
       </c>
       <c r="B734" s="128" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -17769,7 +17772,7 @@
         <v>1501</v>
       </c>
       <c r="B735" s="128" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -17777,7 +17780,7 @@
         <v>1501</v>
       </c>
       <c r="B736" s="128" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -17785,7 +17788,7 @@
         <v>1501</v>
       </c>
       <c r="B737" s="128" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -17793,7 +17796,7 @@
         <v>1501</v>
       </c>
       <c r="B738" s="128" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -17801,7 +17804,7 @@
         <v>1501</v>
       </c>
       <c r="B739" s="128" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -17809,7 +17812,7 @@
         <v>1501</v>
       </c>
       <c r="B740" s="128" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -17817,7 +17820,7 @@
         <v>1501</v>
       </c>
       <c r="B741" s="128" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -17825,7 +17828,7 @@
         <v>1501</v>
       </c>
       <c r="B742" s="128" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -17833,7 +17836,7 @@
         <v>1501</v>
       </c>
       <c r="B743" s="128" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -17841,7 +17844,7 @@
         <v>1501</v>
       </c>
       <c r="B744" s="128" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -17849,7 +17852,7 @@
         <v>1501</v>
       </c>
       <c r="B745" s="128" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -17857,7 +17860,7 @@
         <v>1501</v>
       </c>
       <c r="B746" s="128" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -17865,7 +17868,7 @@
         <v>1501</v>
       </c>
       <c r="B747" s="128" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -17873,15 +17876,15 @@
         <v>1501</v>
       </c>
       <c r="B748" s="128" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" s="128" t="s">
-        <v>136</v>
+        <v>1501</v>
       </c>
       <c r="B749" s="128" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -17889,7 +17892,7 @@
         <v>136</v>
       </c>
       <c r="B750" s="128" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -17897,7 +17900,7 @@
         <v>136</v>
       </c>
       <c r="B751" s="128" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -17905,7 +17908,7 @@
         <v>136</v>
       </c>
       <c r="B752" s="128" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -17913,7 +17916,7 @@
         <v>136</v>
       </c>
       <c r="B753" s="128" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -17921,7 +17924,7 @@
         <v>136</v>
       </c>
       <c r="B754" s="128" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -17929,7 +17932,7 @@
         <v>136</v>
       </c>
       <c r="B755" s="128" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -17937,7 +17940,7 @@
         <v>136</v>
       </c>
       <c r="B756" s="128" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -17945,7 +17948,7 @@
         <v>136</v>
       </c>
       <c r="B757" s="128" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -17953,7 +17956,7 @@
         <v>136</v>
       </c>
       <c r="B758" s="128" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -17961,7 +17964,7 @@
         <v>136</v>
       </c>
       <c r="B759" s="128" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -17969,7 +17972,7 @@
         <v>136</v>
       </c>
       <c r="B760" s="128" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -17977,7 +17980,7 @@
         <v>136</v>
       </c>
       <c r="B761" s="128" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -17985,7 +17988,7 @@
         <v>136</v>
       </c>
       <c r="B762" s="128" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -17993,7 +17996,7 @@
         <v>136</v>
       </c>
       <c r="B763" s="128" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -18001,7 +18004,7 @@
         <v>136</v>
       </c>
       <c r="B764" s="128" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -18009,7 +18012,7 @@
         <v>136</v>
       </c>
       <c r="B765" s="128" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -18017,7 +18020,7 @@
         <v>136</v>
       </c>
       <c r="B766" s="128" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -18025,15 +18028,15 @@
         <v>136</v>
       </c>
       <c r="B767" s="128" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" s="128" t="s">
-        <v>1536</v>
+        <v>136</v>
       </c>
       <c r="B768" s="128" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -18041,7 +18044,7 @@
         <v>1536</v>
       </c>
       <c r="B769" s="128" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -18049,7 +18052,7 @@
         <v>1536</v>
       </c>
       <c r="B770" s="128" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -18057,7 +18060,7 @@
         <v>1536</v>
       </c>
       <c r="B771" s="128" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -18065,7 +18068,7 @@
         <v>1536</v>
       </c>
       <c r="B772" s="128" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -18073,7 +18076,7 @@
         <v>1536</v>
       </c>
       <c r="B773" s="128" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -18081,7 +18084,7 @@
         <v>1536</v>
       </c>
       <c r="B774" s="128" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -18089,7 +18092,7 @@
         <v>1536</v>
       </c>
       <c r="B775" s="128" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -18097,7 +18100,7 @@
         <v>1536</v>
       </c>
       <c r="B776" s="128" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -18105,7 +18108,7 @@
         <v>1536</v>
       </c>
       <c r="B777" s="128" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -18113,7 +18116,7 @@
         <v>1536</v>
       </c>
       <c r="B778" s="128" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -18121,7 +18124,7 @@
         <v>1536</v>
       </c>
       <c r="B779" s="128" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -18129,7 +18132,7 @@
         <v>1536</v>
       </c>
       <c r="B780" s="128" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -18137,7 +18140,7 @@
         <v>1536</v>
       </c>
       <c r="B781" s="128" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -18145,7 +18148,7 @@
         <v>1536</v>
       </c>
       <c r="B782" s="128" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -18153,15 +18156,15 @@
         <v>1536</v>
       </c>
       <c r="B783" s="128" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" s="128" t="s">
-        <v>1553</v>
+        <v>1536</v>
       </c>
       <c r="B784" s="128" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -18169,7 +18172,7 @@
         <v>1553</v>
       </c>
       <c r="B785" s="128" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -18177,7 +18180,7 @@
         <v>1553</v>
       </c>
       <c r="B786" s="128" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -18185,7 +18188,7 @@
         <v>1553</v>
       </c>
       <c r="B787" s="128" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -18193,7 +18196,7 @@
         <v>1553</v>
       </c>
       <c r="B788" s="128" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -18201,7 +18204,7 @@
         <v>1553</v>
       </c>
       <c r="B789" s="128" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -18209,7 +18212,7 @@
         <v>1553</v>
       </c>
       <c r="B790" s="128" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -18217,7 +18220,7 @@
         <v>1553</v>
       </c>
       <c r="B791" s="128" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="792" spans="1:2">
@@ -18225,7 +18228,7 @@
         <v>1553</v>
       </c>
       <c r="B792" s="128" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="793" spans="1:2">
@@ -18233,7 +18236,7 @@
         <v>1553</v>
       </c>
       <c r="B793" s="128" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -18241,7 +18244,7 @@
         <v>1553</v>
       </c>
       <c r="B794" s="128" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="795" spans="1:2">
@@ -18249,7 +18252,7 @@
         <v>1553</v>
       </c>
       <c r="B795" s="128" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="796" spans="1:2">
@@ -18257,7 +18260,7 @@
         <v>1553</v>
       </c>
       <c r="B796" s="128" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="797" spans="1:2">
@@ -18265,7 +18268,7 @@
         <v>1553</v>
       </c>
       <c r="B797" s="128" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="798" spans="1:2">
@@ -18273,7 +18276,7 @@
         <v>1553</v>
       </c>
       <c r="B798" s="128" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="799" spans="1:2">
@@ -18281,7 +18284,7 @@
         <v>1553</v>
       </c>
       <c r="B799" s="128" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -18289,15 +18292,15 @@
         <v>1553</v>
       </c>
       <c r="B800" s="128" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" s="128" t="s">
-        <v>123</v>
+        <v>1553</v>
       </c>
       <c r="B801" s="128" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -18305,7 +18308,7 @@
         <v>123</v>
       </c>
       <c r="B802" s="128" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -18313,7 +18316,7 @@
         <v>123</v>
       </c>
       <c r="B803" s="128" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="804" spans="1:2">
@@ -18321,7 +18324,7 @@
         <v>123</v>
       </c>
       <c r="B804" s="128" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="805" spans="1:2">
@@ -18329,7 +18332,7 @@
         <v>123</v>
       </c>
       <c r="B805" s="128" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -18337,7 +18340,7 @@
         <v>123</v>
       </c>
       <c r="B806" s="128" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -18345,7 +18348,7 @@
         <v>123</v>
       </c>
       <c r="B807" s="128" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -18353,7 +18356,7 @@
         <v>123</v>
       </c>
       <c r="B808" s="128" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -18361,7 +18364,7 @@
         <v>123</v>
       </c>
       <c r="B809" s="128" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -18369,7 +18372,7 @@
         <v>123</v>
       </c>
       <c r="B810" s="128" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -18377,7 +18380,7 @@
         <v>123</v>
       </c>
       <c r="B811" s="128" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -18385,7 +18388,7 @@
         <v>123</v>
       </c>
       <c r="B812" s="128" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="813" spans="1:2">
@@ -18393,7 +18396,7 @@
         <v>123</v>
       </c>
       <c r="B813" s="128" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="814" spans="1:2">
@@ -18401,7 +18404,7 @@
         <v>123</v>
       </c>
       <c r="B814" s="128" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="815" spans="1:2">
@@ -18409,7 +18412,7 @@
         <v>123</v>
       </c>
       <c r="B815" s="128" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -18417,7 +18420,7 @@
         <v>123</v>
       </c>
       <c r="B816" s="128" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -18425,6 +18428,14 @@
         <v>123</v>
       </c>
       <c r="B817" s="128" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818" s="128" t="s">
+        <v>123</v>
+      </c>
+      <c r="B818" s="128" t="s">
         <v>1587</v>
       </c>
     </row>
@@ -18442,7 +18453,7 @@
     <tabColor rgb="FF607D8B"/>
   </sheetPr>
   <dimension ref="A1:M88"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -18452,20 +18463,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="44.1" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="35" t="s">
@@ -21466,27 +21477,27 @@
     <tabColor rgb="FF607D8B"/>
   </sheetPr>
   <dimension ref="A1:J497"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="44.1" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-    </row>
-    <row r="2" spans="1:10" ht="21.95" customHeight="1">
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+    </row>
+    <row r="2" spans="1:10" ht="21.9" customHeight="1">
       <c r="A2" s="114" t="s">
         <v>193</v>
       </c>
@@ -35884,28 +35895,28 @@
     <tabColor rgb="FFE67E22"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="44.1" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>1595</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
     </row>
     <row r="2" spans="1:3" ht="27" customHeight="1">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="172" t="s">
         <v>1597</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-    </row>
-    <row r="3" spans="1:3" ht="27.95" customHeight="1">
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+    </row>
+    <row r="3" spans="1:3" ht="27.9" customHeight="1">
       <c r="A3" s="30" t="s">
         <v>34</v>
       </c>
@@ -35916,20 +35927,20 @@
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="27.95" customHeight="1">
+    <row r="4" spans="1:3" ht="27.9" customHeight="1">
       <c r="A4" s="32" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="33"/>
       <c r="C4" s="33"/>
     </row>
-    <row r="5" spans="1:3" ht="27.95" customHeight="1">
+    <row r="5" spans="1:3" ht="27.9" customHeight="1">
       <c r="A5" s="34" t="str">
         <f>'Apostas - Grupos'!A5</f>
         <v>Gustavo Marini</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>1211</v>
+        <v>1618</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>116</v>
@@ -35946,7 +35957,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DA80A566-CE07-4225-9A66-CECC7907350B}">
           <x14:formula1>
-            <xm:f>Jogadores!$B$2:$B$817</xm:f>
+            <xm:f>Jogadores!$B$2:$B$818</xm:f>
           </x14:formula1>
           <xm:sqref>B5</xm:sqref>
         </x14:dataValidation>
@@ -35968,427 +35979,427 @@
     <tabColor rgb="FF922B21"/>
   </sheetPr>
   <dimension ref="A1:BM6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="65" width="13.140625" customWidth="1"/>
+    <col min="2" max="65" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:65" ht="44.1" customHeight="1" thickBot="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>1591</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="145"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="145"/>
-      <c r="Z1" s="145"/>
-      <c r="AA1" s="145"/>
-      <c r="AB1" s="145"/>
-      <c r="AC1" s="145"/>
-      <c r="AD1" s="145"/>
-      <c r="AE1" s="145"/>
-      <c r="AF1" s="145"/>
-      <c r="AG1" s="145"/>
-      <c r="AH1" s="145"/>
-      <c r="AI1" s="145"/>
-      <c r="AJ1" s="145"/>
-      <c r="AK1" s="145"/>
-      <c r="AL1" s="145"/>
-      <c r="AM1" s="145"/>
-      <c r="AN1" s="145"/>
-      <c r="AO1" s="145"/>
-      <c r="AP1" s="145"/>
-      <c r="AQ1" s="145"/>
-      <c r="AR1" s="145"/>
-      <c r="AS1" s="145"/>
-      <c r="AT1" s="145"/>
-      <c r="AU1" s="145"/>
-      <c r="AV1" s="145"/>
-      <c r="AW1" s="145"/>
-      <c r="AX1" s="145"/>
-      <c r="AY1" s="145"/>
-      <c r="AZ1" s="145"/>
-      <c r="BA1" s="145"/>
-      <c r="BB1" s="145"/>
-      <c r="BC1" s="145"/>
-      <c r="BD1" s="145"/>
-      <c r="BE1" s="145"/>
-      <c r="BF1" s="145"/>
-      <c r="BG1" s="145"/>
-      <c r="BH1" s="145"/>
-      <c r="BI1" s="145"/>
-      <c r="BJ1" s="145"/>
-      <c r="BK1" s="145"/>
-      <c r="BL1" s="145"/>
-      <c r="BM1" s="145"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
+      <c r="Y1" s="147"/>
+      <c r="Z1" s="147"/>
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="147"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="147"/>
+      <c r="AH1" s="147"/>
+      <c r="AI1" s="147"/>
+      <c r="AJ1" s="147"/>
+      <c r="AK1" s="147"/>
+      <c r="AL1" s="147"/>
+      <c r="AM1" s="147"/>
+      <c r="AN1" s="147"/>
+      <c r="AO1" s="147"/>
+      <c r="AP1" s="147"/>
+      <c r="AQ1" s="147"/>
+      <c r="AR1" s="147"/>
+      <c r="AS1" s="147"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="147"/>
+      <c r="BA1" s="147"/>
+      <c r="BB1" s="147"/>
+      <c r="BC1" s="147"/>
+      <c r="BD1" s="147"/>
+      <c r="BE1" s="147"/>
+      <c r="BF1" s="147"/>
+      <c r="BG1" s="147"/>
+      <c r="BH1" s="147"/>
+      <c r="BI1" s="147"/>
+      <c r="BJ1" s="147"/>
+      <c r="BK1" s="147"/>
+      <c r="BL1" s="147"/>
+      <c r="BM1" s="147"/>
     </row>
     <row r="2" spans="1:65" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="172" t="s">
         <v>1599</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="170"/>
-      <c r="O2" s="170"/>
-      <c r="P2" s="170"/>
-      <c r="Q2" s="170"/>
-      <c r="R2" s="170"/>
-      <c r="S2" s="170"/>
-      <c r="T2" s="170"/>
-      <c r="U2" s="170"/>
-      <c r="V2" s="170"/>
-      <c r="W2" s="170"/>
-      <c r="X2" s="170"/>
-      <c r="Y2" s="170"/>
-      <c r="Z2" s="170"/>
-      <c r="AA2" s="170"/>
-      <c r="AB2" s="170"/>
-      <c r="AC2" s="170"/>
-      <c r="AD2" s="170"/>
-      <c r="AE2" s="170"/>
-      <c r="AF2" s="170"/>
-      <c r="AG2" s="187"/>
-      <c r="AH2" s="184" t="s">
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="172"/>
+      <c r="S2" s="172"/>
+      <c r="T2" s="172"/>
+      <c r="U2" s="172"/>
+      <c r="V2" s="172"/>
+      <c r="W2" s="172"/>
+      <c r="X2" s="172"/>
+      <c r="Y2" s="172"/>
+      <c r="Z2" s="172"/>
+      <c r="AA2" s="172"/>
+      <c r="AB2" s="172"/>
+      <c r="AC2" s="172"/>
+      <c r="AD2" s="172"/>
+      <c r="AE2" s="172"/>
+      <c r="AF2" s="172"/>
+      <c r="AG2" s="173"/>
+      <c r="AH2" s="169" t="s">
         <v>19</v>
       </c>
-      <c r="AI2" s="185"/>
-      <c r="AJ2" s="185"/>
-      <c r="AK2" s="185"/>
-      <c r="AL2" s="185"/>
-      <c r="AM2" s="185"/>
-      <c r="AN2" s="185"/>
-      <c r="AO2" s="185"/>
-      <c r="AP2" s="185"/>
-      <c r="AQ2" s="185"/>
-      <c r="AR2" s="185"/>
-      <c r="AS2" s="185"/>
-      <c r="AT2" s="185"/>
-      <c r="AU2" s="185"/>
-      <c r="AV2" s="185"/>
-      <c r="AW2" s="186"/>
-      <c r="AX2" s="184" t="s">
+      <c r="AI2" s="170"/>
+      <c r="AJ2" s="170"/>
+      <c r="AK2" s="170"/>
+      <c r="AL2" s="170"/>
+      <c r="AM2" s="170"/>
+      <c r="AN2" s="170"/>
+      <c r="AO2" s="170"/>
+      <c r="AP2" s="170"/>
+      <c r="AQ2" s="170"/>
+      <c r="AR2" s="170"/>
+      <c r="AS2" s="170"/>
+      <c r="AT2" s="170"/>
+      <c r="AU2" s="170"/>
+      <c r="AV2" s="170"/>
+      <c r="AW2" s="171"/>
+      <c r="AX2" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="AY2" s="185"/>
-      <c r="AZ2" s="185"/>
-      <c r="BA2" s="185"/>
-      <c r="BB2" s="185"/>
-      <c r="BC2" s="185"/>
-      <c r="BD2" s="185"/>
-      <c r="BE2" s="186"/>
-      <c r="BF2" s="184" t="s">
+      <c r="AY2" s="170"/>
+      <c r="AZ2" s="170"/>
+      <c r="BA2" s="170"/>
+      <c r="BB2" s="170"/>
+      <c r="BC2" s="170"/>
+      <c r="BD2" s="170"/>
+      <c r="BE2" s="171"/>
+      <c r="BF2" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="BG2" s="185"/>
-      <c r="BH2" s="185"/>
-      <c r="BI2" s="186"/>
-      <c r="BJ2" s="180" t="s">
+      <c r="BG2" s="170"/>
+      <c r="BH2" s="170"/>
+      <c r="BI2" s="171"/>
+      <c r="BJ2" s="165" t="s">
         <v>1614</v>
       </c>
-      <c r="BK2" s="181"/>
-      <c r="BL2" s="182" t="s">
+      <c r="BK2" s="166"/>
+      <c r="BL2" s="167" t="s">
         <v>1613</v>
       </c>
-      <c r="BM2" s="183"/>
-    </row>
-    <row r="3" spans="1:65" ht="21.95" customHeight="1">
+      <c r="BM2" s="168"/>
+    </row>
+    <row r="3" spans="1:65" ht="21.9" customHeight="1">
       <c r="A3" s="119" t="s">
         <v>709</v>
       </c>
-      <c r="B3" s="189" t="s">
+      <c r="B3" s="151" t="s">
         <v>710</v>
       </c>
-      <c r="C3" s="145"/>
-      <c r="D3" s="189" t="s">
+      <c r="C3" s="147"/>
+      <c r="D3" s="151" t="s">
         <v>711</v>
       </c>
-      <c r="E3" s="145"/>
-      <c r="F3" s="189" t="s">
+      <c r="E3" s="147"/>
+      <c r="F3" s="151" t="s">
         <v>712</v>
       </c>
-      <c r="G3" s="145"/>
-      <c r="H3" s="189" t="s">
+      <c r="G3" s="147"/>
+      <c r="H3" s="151" t="s">
         <v>713</v>
       </c>
-      <c r="I3" s="145"/>
-      <c r="J3" s="189" t="s">
+      <c r="I3" s="147"/>
+      <c r="J3" s="151" t="s">
         <v>714</v>
       </c>
-      <c r="K3" s="145"/>
-      <c r="L3" s="189" t="s">
+      <c r="K3" s="147"/>
+      <c r="L3" s="151" t="s">
         <v>715</v>
       </c>
-      <c r="M3" s="145"/>
-      <c r="N3" s="189" t="s">
+      <c r="M3" s="147"/>
+      <c r="N3" s="151" t="s">
         <v>716</v>
       </c>
-      <c r="O3" s="145"/>
-      <c r="P3" s="189" t="s">
+      <c r="O3" s="147"/>
+      <c r="P3" s="151" t="s">
         <v>717</v>
       </c>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="189" t="s">
+      <c r="Q3" s="147"/>
+      <c r="R3" s="151" t="s">
         <v>718</v>
       </c>
-      <c r="S3" s="145"/>
-      <c r="T3" s="189" t="s">
+      <c r="S3" s="147"/>
+      <c r="T3" s="151" t="s">
         <v>719</v>
       </c>
-      <c r="U3" s="145"/>
-      <c r="V3" s="189" t="s">
+      <c r="U3" s="147"/>
+      <c r="V3" s="151" t="s">
         <v>720</v>
       </c>
-      <c r="W3" s="145"/>
-      <c r="X3" s="189" t="s">
+      <c r="W3" s="147"/>
+      <c r="X3" s="151" t="s">
         <v>721</v>
       </c>
-      <c r="Y3" s="145"/>
-      <c r="Z3" s="189" t="s">
+      <c r="Y3" s="147"/>
+      <c r="Z3" s="151" t="s">
         <v>722</v>
       </c>
-      <c r="AA3" s="145"/>
-      <c r="AB3" s="189" t="s">
+      <c r="AA3" s="147"/>
+      <c r="AB3" s="151" t="s">
         <v>723</v>
       </c>
-      <c r="AC3" s="145"/>
-      <c r="AD3" s="189" t="s">
+      <c r="AC3" s="147"/>
+      <c r="AD3" s="151" t="s">
         <v>724</v>
       </c>
-      <c r="AE3" s="145"/>
-      <c r="AF3" s="189" t="s">
+      <c r="AE3" s="147"/>
+      <c r="AF3" s="151" t="s">
         <v>725</v>
       </c>
-      <c r="AG3" s="145"/>
-      <c r="AH3" s="191" t="s">
+      <c r="AG3" s="147"/>
+      <c r="AH3" s="163" t="s">
         <v>726</v>
       </c>
-      <c r="AI3" s="145"/>
-      <c r="AJ3" s="192" t="s">
+      <c r="AI3" s="147"/>
+      <c r="AJ3" s="156" t="s">
         <v>727</v>
       </c>
-      <c r="AK3" s="145"/>
-      <c r="AL3" s="192" t="s">
+      <c r="AK3" s="147"/>
+      <c r="AL3" s="156" t="s">
         <v>728</v>
       </c>
-      <c r="AM3" s="145"/>
-      <c r="AN3" s="192" t="s">
+      <c r="AM3" s="147"/>
+      <c r="AN3" s="156" t="s">
         <v>729</v>
       </c>
-      <c r="AO3" s="145"/>
-      <c r="AP3" s="192" t="s">
+      <c r="AO3" s="147"/>
+      <c r="AP3" s="156" t="s">
         <v>730</v>
       </c>
-      <c r="AQ3" s="145"/>
-      <c r="AR3" s="192" t="s">
+      <c r="AQ3" s="147"/>
+      <c r="AR3" s="156" t="s">
         <v>731</v>
       </c>
-      <c r="AS3" s="145"/>
-      <c r="AT3" s="192" t="s">
+      <c r="AS3" s="147"/>
+      <c r="AT3" s="156" t="s">
         <v>732</v>
       </c>
-      <c r="AU3" s="145"/>
-      <c r="AV3" s="192" t="s">
+      <c r="AU3" s="147"/>
+      <c r="AV3" s="156" t="s">
         <v>733</v>
       </c>
-      <c r="AW3" s="194"/>
-      <c r="AX3" s="195" t="s">
+      <c r="AW3" s="145"/>
+      <c r="AX3" s="164" t="s">
         <v>734</v>
       </c>
-      <c r="AY3" s="145"/>
-      <c r="AZ3" s="196" t="s">
+      <c r="AY3" s="147"/>
+      <c r="AZ3" s="153" t="s">
         <v>735</v>
       </c>
-      <c r="BA3" s="145"/>
-      <c r="BB3" s="196" t="s">
+      <c r="BA3" s="147"/>
+      <c r="BB3" s="153" t="s">
         <v>736</v>
       </c>
-      <c r="BC3" s="145"/>
-      <c r="BD3" s="196" t="s">
+      <c r="BC3" s="147"/>
+      <c r="BD3" s="153" t="s">
         <v>737</v>
       </c>
-      <c r="BE3" s="194"/>
-      <c r="BF3" s="205" t="s">
+      <c r="BE3" s="145"/>
+      <c r="BF3" s="148" t="s">
         <v>738</v>
       </c>
-      <c r="BG3" s="145"/>
-      <c r="BH3" s="206" t="s">
+      <c r="BG3" s="147"/>
+      <c r="BH3" s="149" t="s">
         <v>739</v>
       </c>
-      <c r="BI3" s="194"/>
-      <c r="BJ3" s="200" t="s">
+      <c r="BI3" s="145"/>
+      <c r="BJ3" s="152" t="s">
         <v>740</v>
       </c>
-      <c r="BK3" s="194"/>
-      <c r="BL3" s="204" t="s">
+      <c r="BK3" s="145"/>
+      <c r="BL3" s="144" t="s">
         <v>741</v>
       </c>
-      <c r="BM3" s="194"/>
-    </row>
-    <row r="4" spans="1:65" ht="15.95" customHeight="1">
+      <c r="BM3" s="145"/>
+    </row>
+    <row r="4" spans="1:65" ht="15.9" customHeight="1">
       <c r="A4" s="120" t="s">
         <v>742</v>
       </c>
-      <c r="B4" s="188">
+      <c r="B4" s="150">
         <v>46201</v>
       </c>
-      <c r="C4" s="145"/>
-      <c r="D4" s="188">
+      <c r="C4" s="147"/>
+      <c r="D4" s="150">
         <v>46202</v>
       </c>
-      <c r="E4" s="145"/>
-      <c r="F4" s="188">
+      <c r="E4" s="147"/>
+      <c r="F4" s="150">
         <v>46202</v>
       </c>
-      <c r="G4" s="145"/>
-      <c r="H4" s="188">
+      <c r="G4" s="147"/>
+      <c r="H4" s="150">
         <v>46202</v>
       </c>
-      <c r="I4" s="145"/>
-      <c r="J4" s="188">
+      <c r="I4" s="147"/>
+      <c r="J4" s="150">
         <v>46203</v>
       </c>
-      <c r="K4" s="145"/>
-      <c r="L4" s="188">
+      <c r="K4" s="147"/>
+      <c r="L4" s="150">
         <v>46203</v>
       </c>
-      <c r="M4" s="145"/>
-      <c r="N4" s="188">
+      <c r="M4" s="147"/>
+      <c r="N4" s="150">
         <v>46203</v>
       </c>
-      <c r="O4" s="145"/>
-      <c r="P4" s="188">
+      <c r="O4" s="147"/>
+      <c r="P4" s="150">
         <v>46204</v>
       </c>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="188">
+      <c r="Q4" s="147"/>
+      <c r="R4" s="150">
         <v>46204</v>
       </c>
-      <c r="S4" s="145"/>
-      <c r="T4" s="188">
+      <c r="S4" s="147"/>
+      <c r="T4" s="150">
         <v>46204</v>
       </c>
-      <c r="U4" s="145"/>
-      <c r="V4" s="188">
+      <c r="U4" s="147"/>
+      <c r="V4" s="150">
         <v>46205</v>
       </c>
-      <c r="W4" s="145"/>
-      <c r="X4" s="188">
+      <c r="W4" s="147"/>
+      <c r="X4" s="150">
         <v>46205</v>
       </c>
-      <c r="Y4" s="145"/>
-      <c r="Z4" s="188">
+      <c r="Y4" s="147"/>
+      <c r="Z4" s="150">
         <v>46205</v>
       </c>
-      <c r="AA4" s="145"/>
-      <c r="AB4" s="188">
+      <c r="AA4" s="147"/>
+      <c r="AB4" s="150">
         <v>46206</v>
       </c>
-      <c r="AC4" s="145"/>
-      <c r="AD4" s="188">
+      <c r="AC4" s="147"/>
+      <c r="AD4" s="150">
         <v>46206</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="188">
+      <c r="AE4" s="147"/>
+      <c r="AF4" s="150">
         <v>46206</v>
       </c>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="202">
+      <c r="AG4" s="147"/>
+      <c r="AH4" s="155">
         <v>46207</v>
       </c>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="193">
+      <c r="AI4" s="147"/>
+      <c r="AJ4" s="146">
         <v>46207</v>
       </c>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="193">
+      <c r="AK4" s="147"/>
+      <c r="AL4" s="146">
         <v>46208</v>
       </c>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="193">
+      <c r="AM4" s="147"/>
+      <c r="AN4" s="146">
         <v>46208</v>
       </c>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="193">
+      <c r="AO4" s="147"/>
+      <c r="AP4" s="146">
         <v>46209</v>
       </c>
-      <c r="AQ4" s="145"/>
-      <c r="AR4" s="193">
+      <c r="AQ4" s="147"/>
+      <c r="AR4" s="146">
         <v>46209</v>
       </c>
-      <c r="AS4" s="145"/>
-      <c r="AT4" s="193">
+      <c r="AS4" s="147"/>
+      <c r="AT4" s="146">
         <v>46210</v>
       </c>
-      <c r="AU4" s="145"/>
-      <c r="AV4" s="193">
+      <c r="AU4" s="147"/>
+      <c r="AV4" s="146">
         <v>46210</v>
       </c>
-      <c r="AW4" s="194"/>
-      <c r="AX4" s="190">
+      <c r="AW4" s="145"/>
+      <c r="AX4" s="162">
         <v>46212</v>
       </c>
-      <c r="AY4" s="145"/>
-      <c r="AZ4" s="197">
+      <c r="AY4" s="147"/>
+      <c r="AZ4" s="159">
         <v>46213</v>
       </c>
-      <c r="BA4" s="145"/>
-      <c r="BB4" s="197">
+      <c r="BA4" s="147"/>
+      <c r="BB4" s="159">
         <v>46214</v>
       </c>
-      <c r="BC4" s="145"/>
-      <c r="BD4" s="197">
+      <c r="BC4" s="147"/>
+      <c r="BD4" s="159">
         <v>46214</v>
       </c>
-      <c r="BE4" s="194"/>
-      <c r="BF4" s="198">
+      <c r="BE4" s="145"/>
+      <c r="BF4" s="160">
         <v>46217</v>
       </c>
-      <c r="BG4" s="145"/>
-      <c r="BH4" s="201">
+      <c r="BG4" s="147"/>
+      <c r="BH4" s="154">
         <v>46218</v>
       </c>
-      <c r="BI4" s="194"/>
-      <c r="BJ4" s="203">
+      <c r="BI4" s="145"/>
+      <c r="BJ4" s="157">
         <v>46221</v>
       </c>
-      <c r="BK4" s="194"/>
-      <c r="BL4" s="199">
+      <c r="BK4" s="145"/>
+      <c r="BL4" s="161">
         <v>46222</v>
       </c>
-      <c r="BM4" s="194"/>
-    </row>
-    <row r="5" spans="1:65" ht="21.95" customHeight="1">
+      <c r="BM4" s="145"/>
+    </row>
+    <row r="5" spans="1:65" ht="21.9" customHeight="1">
       <c r="A5" s="34" t="str">
         <f>'Apostas - Grupos'!A5</f>
         <v>Gustavo Marini</v>
@@ -36785,11 +36796,56 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BJ2:BK2"/>
+    <mergeCell ref="BL2:BM2"/>
+    <mergeCell ref="BF2:BI2"/>
+    <mergeCell ref="AH2:AW2"/>
+    <mergeCell ref="A2:AG2"/>
+    <mergeCell ref="AX2:BE2"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="AB3:AC3"/>
@@ -36806,56 +36862,11 @@
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
     <mergeCell ref="BJ4:BK4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="BJ2:BK2"/>
-    <mergeCell ref="BL2:BM2"/>
-    <mergeCell ref="BF2:BI2"/>
-    <mergeCell ref="AH2:AW2"/>
-    <mergeCell ref="A2:AG2"/>
-    <mergeCell ref="AX2:BE2"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
